--- a/data/macro/USA/USCPI YoY.xlsx
+++ b/data/macro/USA/USCPI YoY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7A0FFE-3F89-454E-B598-1CDF90F3E91D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B692473A-BBFE-4306-90EA-482D05176B8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="780" windowWidth="30375" windowHeight="20445" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
   </bookViews>
@@ -63,7 +63,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -188,10 +188,10 @@
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -14511,6 +14511,12 @@
       <c r="D675" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="E675" s="9">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F675" s="9">
+        <v>2.4E-2</v>
+      </c>
       <c r="G675" s="9">
         <v>2.4E-2</v>
       </c>

--- a/data/macro/USA/USCPI YoY.xlsx
+++ b/data/macro/USA/USCPI YoY.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B692473A-BBFE-4306-90EA-482D05176B8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DD9525-9590-41F0-95D3-F5858DD38528}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="780" windowWidth="30375" windowHeight="20445" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="fig" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -213,6 +214,4889 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>data!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>data!$B$2:$B$675</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="674"/>
+                <c:pt idx="0">
+                  <c:v>25587</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25618</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25647</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25680</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25708</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25737</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25770</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25801</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25834</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25862</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25896</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25926</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25962</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>25983</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>26011</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26044</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26074</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26105</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26137</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26165</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>26198</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26228</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26256</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26289</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>26319</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26352</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26381</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>26410</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>26438</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>26471</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>26501</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26533</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26564</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26592</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>26624</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26655</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26687</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>26717</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>26744</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26774</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>26806</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>26836</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>26865</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>26897</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>26928</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>26956</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>26989</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>27019</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>27051</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>27082</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>27109</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>27138</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>27170</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>27201</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>27229</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>27262</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>27292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>27324</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>27354</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>27383</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>27415</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>27446</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>27473</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>27506</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>27535</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>27565</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>27597</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>27627</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>27656</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>27689</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>27718</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>27747</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27780</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>27810</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>27838</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>27871</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>27901</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>27933</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>27962</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>27992</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>28024</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>28054</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>28083</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>28115</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>28144</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>28174</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>28202</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>28236</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>28265</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>28297</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>28327</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>28356</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>28389</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>28419</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>28451</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>28480</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>28510</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>28548</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>28577</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>28608</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>28641</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>28671</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>28699</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>28731</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>28759</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28789</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>28822</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>28846</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>28879</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>28909</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28937</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>28971</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>29032</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>29062</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>29091</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>29123</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>29154</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>29186</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>29210</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>29245</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>29273</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>29305</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>29333</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>29364</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>29396</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>29425</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>29455</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>29487</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>29518</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>29550</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>29578</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>29609</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>29642</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>29669</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>29699</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>29728</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>29760</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>29790</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>29823</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>29853</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>29882</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>29914</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>29942</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>29973</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>30007</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>30033</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>30064</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>30092</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>30124</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>30155</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>30187</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>30217</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>30250</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>30278</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>30306</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>30337</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>30372</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>30398</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>30428</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>30460</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>30489</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>30519</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>30551</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>30582</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>30614</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>30643</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>30671</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>30705</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>30736</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>30764</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>30796</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>30824</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>30855</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>30887</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>30916</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>30946</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>30979</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>31007</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>31036</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>31070</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>31104</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>31128</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>31160</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>31188</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>31218</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>31251</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>31281</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>31314</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>31343</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>31373</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>31401</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>31434</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>31468</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>31496</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>31524</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>31553</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>31583</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>31616</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>31645</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>31678</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>31708</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>31741</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>31765</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>31798</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>31835</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>31863</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>31891</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>31919</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>31951</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>31980</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>32010</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>32043</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>32073</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>32101</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>32129</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>32162</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>32199</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>32225</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>32253</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>32283</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>32315</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>32346</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>32378</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>32407</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>32437</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>32469</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>32497</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>32527</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>32561</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>32588</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>32616</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>32646</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>32675</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>32708</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>32738</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>32770</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>32800</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>32833</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>32861</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>32891</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>32925</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>32952</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>32980</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>33009</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>33039</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>33072</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>33101</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>33134</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>33164</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>33193</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>33225</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>33254</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>33289</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>33316</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>33340</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>33372</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>33403</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>33436</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>33464</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>33494</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>33528</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>33556</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>33585</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>33619</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>33653</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>33680</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>33704</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>33737</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>33767</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>33799</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>33829</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>33862</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>33892</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>33921</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>33951</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>33984</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>34018</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>34045</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>34068</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>34102</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>34135</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>34164</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>34194</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>34226</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>34257</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>34283</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>34313</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>34347</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>34382</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>34409</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>34437</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>34467</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>34499</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>34528</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>34558</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>34590</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>34621</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>34654</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>34682</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>34710</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>34745</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>34774</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>34801</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>34831</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>34863</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>34894</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>34922</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>34955</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>34985</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>35018</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>35047</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>35096</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>35123</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>35139</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>35167</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>35199</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>35228</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>35262</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>35290</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>35321</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>35354</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>35383</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>35411</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>35444</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>35480</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>35508</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>35535</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>35565</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>35598</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>35627</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>35656</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>35689</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>35719</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>35752</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>35780</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>35808</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>35850</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>35873</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>35899</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>35929</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>35962</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>35990</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>36025</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>36055</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>36084</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>36116</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>36144</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>36174</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>36210</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>36237</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>36263</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>36294</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>36327</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>36356</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>36389</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>36418</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>36452</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>36481</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>36508</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>36539</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>36574</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>36602</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>36630</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>36662</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>36691</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>36725</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>36754</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>36784</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>36817</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>36846</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>36875</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>36908</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>36943</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>36971</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>36998</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>37027</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>37057</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>37090</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>37119</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>37152</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>37183</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>37211</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>37239</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>37272</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>37307</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>37336</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>37362</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>37391</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>37425</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>37456</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>37484</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>37517</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>37547</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>37579</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>37607</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>37637</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>37673</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>37701</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>37727</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>37757</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>37789</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>37818</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>37848</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>37880</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>37910</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>37943</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>37971</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>38001</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>38037</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>38063</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>38091</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>38121</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>38153</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>38184</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>38216</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>38246</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>38279</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>38308</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>38338</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>38371</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>38406</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>38434</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>38462</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>38490</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>38518</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>38547</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>38580</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>38610</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>38639</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>38672</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>38701</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>38735</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>38770</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>38792</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>38826</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>38854</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>38882</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>38917</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>38945</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>38975</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>39008</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>39037</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>39066</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>39100</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>39134</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>39157</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>39189</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>39217</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>39248</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>39281</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>39309</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>39344</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>39372</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>39401</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>39430</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>39463</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>39498</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>39521</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>39554</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>39582</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>39612</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>39645</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>39674</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>39707</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>39737</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>39771</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>39798</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>39829</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>39864</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>39890</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>39918</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>39948</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>39981</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>40009</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>40039</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>40072</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>40101</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>40135</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>40163</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>40193</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>40228</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>40255</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>40282</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>40317</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>40346</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>40375</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>40403</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>40438</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>40466</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>40499</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>40527</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>40557</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>40591</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>40619</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>40648</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>40676</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>40709</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>40739</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>40773</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>40801</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>40835</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>40863</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>40893</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>40927</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>40956</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>40984</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>41012</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>41044</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>41074</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>41107</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>41136</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>41166</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>41198</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>41228</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>41257</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>41290</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>41326</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>41348</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>41380</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>41410</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>41443</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>41471</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>41501</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>41534</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>41577</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>41598</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>41625</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>41655</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>41690</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>41716</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>41744</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>41774</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>41807</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>41842</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>41870</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>41899</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>41934</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>41963</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>41990</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>42020</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>42061</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>42087</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>42111</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>42146</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>42173</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>42202</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>42235</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>42263</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>42292</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>42325</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>42353</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>42389</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>42419</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>42445</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>42474</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>42507</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>42537</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>42566</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>42598</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>42629</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>42661</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>42691</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>42719</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>42753</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>42781</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>42809</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>42839</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>42867</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>42900</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>42930</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>42958</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>42992</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>43021</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>43054</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>43082</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>43112</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>43145</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>43172</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>43201</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>43230</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>43263</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>43293</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>43322</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>43356</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>43384</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>43418</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>43446</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>43476</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>43509</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>43536</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>43565</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>43595</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>43628</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>43657</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>43690</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>43720</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>43748</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>43782</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>43810</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>43844</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>43874</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>43901</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>43931</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>43963</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>43992</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>44026</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>44055</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>44085</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>44117</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>44147</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>44175</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>44209</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>44237</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>44265</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>44299</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>44328</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>44357</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>44390</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>44419</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>44453</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>44482</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>44510</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>44540</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>44573</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>44602</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>44630</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>44663</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>44692</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>44722</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>44755</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>44783</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>44817</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>44847</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>44875</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>44908</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>44938</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>44971</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>44999</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>45028</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>45056</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>45090</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>45119</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>45148</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>45182</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>45211</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>45244</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>45272</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>45302</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>45335</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>45363</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>45392</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>45427</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>45455</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>45484</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>45518</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>45546</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>45609</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>45637</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>45672</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>45700</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>45728</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>45790</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>45819</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>45853</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>45911</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>45954</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>46009</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>46092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>data!$E$2:$E$675</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="674"/>
+                <c:pt idx="0">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8.6999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.107</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.123</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.10299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.13900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.14199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.14399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.14399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.13100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.129</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.128</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.11799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>-4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>-7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>-1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>-2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>-1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-393D-4C96-A35C-A8EA38DA8486}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1775995792"/>
+        <c:axId val="1172243136"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1775995792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="40179"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1172243136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1172243136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.1"/>
+          <c:min val="-1.0000000000000002E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1775995792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51815F05-AFB9-4AA3-B2B1-01345F72A369}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14526,4 +19410,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EBF4DF-B181-4399-AF18-DD9803B9FC52}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/macro/USA/USCPI YoY.xlsx
+++ b/data/macro/USA/USCPI YoY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DD9525-9590-41F0-95D3-F5858DD38528}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4DC65F-2957-4E0B-AADD-77FC3F33EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="780" windowWidth="30375" windowHeight="20445" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="9">
   <si>
     <t>Release Date</t>
   </si>
@@ -233,8 +233,9 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -251,23 +252,23 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="15875">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>data!$B$2:$B$675</c:f>
+              <c:f>data!$B$2:$B$1675</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="674"/>
+                <c:ptCount val="1674"/>
                 <c:pt idx="0">
                   <c:v>25587</c:v>
                 </c:pt>
@@ -2289,16 +2290,19 @@
                 </c:pt>
                 <c:pt idx="673">
                   <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>46122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>data!$E$2:$E$675</c:f>
+              <c:f>data!$E$2:$E$1675</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="674"/>
+                <c:ptCount val="1674"/>
                 <c:pt idx="0">
                   <c:v>6.2E-2</c:v>
                 </c:pt>
@@ -4320,11 +4324,13 @@
                 </c:pt>
                 <c:pt idx="673">
                   <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>3.3000000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-393D-4C96-A35C-A8EA38DA8486}"/>
@@ -4339,10 +4345,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
+        <c:gapWidth val="150"/>
         <c:axId val="1775995792"/>
         <c:axId val="1172243136"/>
-      </c:lineChart>
+      </c:barChart>
       <c:dateAx>
         <c:axId val="1775995792"/>
         <c:scaling>
@@ -4463,6 +4469,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4470,7 +4477,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5396,18 +5402,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCC3F54-AD1C-4CCF-B8C0-3F784AA58BEE}">
-  <dimension ref="A1:G675"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G676"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.42578125" style="9" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="5"/>
+    <col min="5" max="7" width="11.44140625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>25538</v>
       </c>
@@ -5447,7 +5453,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>25569</v>
       </c>
@@ -5467,7 +5473,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>25600</v>
       </c>
@@ -5487,7 +5493,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>25628</v>
       </c>
@@ -5507,7 +5513,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>25659</v>
       </c>
@@ -5527,7 +5533,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>25689</v>
       </c>
@@ -5547,7 +5553,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>25720</v>
       </c>
@@ -5567,7 +5573,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>25750</v>
       </c>
@@ -5587,7 +5593,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>25781</v>
       </c>
@@ -5607,7 +5613,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25812</v>
       </c>
@@ -5627,7 +5633,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>25842</v>
       </c>
@@ -5647,7 +5653,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>25873</v>
       </c>
@@ -5667,7 +5673,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>25903</v>
       </c>
@@ -5687,7 +5693,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>25934</v>
       </c>
@@ -5707,7 +5713,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>25965</v>
       </c>
@@ -5727,7 +5733,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>25993</v>
       </c>
@@ -5747,7 +5753,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>26024</v>
       </c>
@@ -5767,7 +5773,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>26054</v>
       </c>
@@ -5787,7 +5793,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>26085</v>
       </c>
@@ -5807,7 +5813,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>26115</v>
       </c>
@@ -5827,7 +5833,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>26146</v>
       </c>
@@ -5847,7 +5853,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>26177</v>
       </c>
@@ -5867,7 +5873,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>26207</v>
       </c>
@@ -5887,7 +5893,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>26238</v>
       </c>
@@ -5907,7 +5913,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26268</v>
       </c>
@@ -5927,7 +5933,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>26299</v>
       </c>
@@ -5947,7 +5953,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>26330</v>
       </c>
@@ -5967,7 +5973,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>26359</v>
       </c>
@@ -5987,7 +5993,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>26390</v>
       </c>
@@ -6007,7 +6013,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>26420</v>
       </c>
@@ -6027,7 +6033,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>26451</v>
       </c>
@@ -6047,7 +6053,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>26481</v>
       </c>
@@ -6067,7 +6073,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>26512</v>
       </c>
@@ -6087,7 +6093,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>26543</v>
       </c>
@@ -6107,7 +6113,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>26573</v>
       </c>
@@ -6127,7 +6133,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>26604</v>
       </c>
@@ -6147,7 +6153,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>26634</v>
       </c>
@@ -6167,7 +6173,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>26665</v>
       </c>
@@ -6187,7 +6193,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>26696</v>
       </c>
@@ -6207,7 +6213,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>26724</v>
       </c>
@@ -6227,7 +6233,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>26755</v>
       </c>
@@ -6247,7 +6253,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>26785</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>26816</v>
       </c>
@@ -6287,7 +6293,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>26846</v>
       </c>
@@ -6307,7 +6313,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>26877</v>
       </c>
@@ -6327,7 +6333,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>26908</v>
       </c>
@@ -6347,7 +6353,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>26938</v>
       </c>
@@ -6367,7 +6373,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>26969</v>
       </c>
@@ -6387,7 +6393,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>26999</v>
       </c>
@@ -6407,7 +6413,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>27030</v>
       </c>
@@ -6427,7 +6433,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>27061</v>
       </c>
@@ -6447,7 +6453,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>27089</v>
       </c>
@@ -6467,7 +6473,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>27120</v>
       </c>
@@ -6487,7 +6493,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>27150</v>
       </c>
@@ -6507,7 +6513,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>27181</v>
       </c>
@@ -6527,7 +6533,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>27211</v>
       </c>
@@ -6547,7 +6553,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>27242</v>
       </c>
@@ -6567,7 +6573,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>27273</v>
       </c>
@@ -6587,7 +6593,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>27303</v>
       </c>
@@ -6607,7 +6613,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>27334</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>27364</v>
       </c>
@@ -6647,7 +6653,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>27395</v>
       </c>
@@ -6667,7 +6673,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>27426</v>
       </c>
@@ -6687,7 +6693,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>27454</v>
       </c>
@@ -6707,7 +6713,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>27485</v>
       </c>
@@ -6727,7 +6733,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>27515</v>
       </c>
@@ -6747,7 +6753,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>27546</v>
       </c>
@@ -6767,7 +6773,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>27576</v>
       </c>
@@ -6787,7 +6793,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>27607</v>
       </c>
@@ -6807,7 +6813,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>27638</v>
       </c>
@@ -6827,7 +6833,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>27668</v>
       </c>
@@ -6847,7 +6853,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>27699</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>27729</v>
       </c>
@@ -6887,7 +6893,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>27760</v>
       </c>
@@ -6907,7 +6913,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>27791</v>
       </c>
@@ -6927,7 +6933,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>27820</v>
       </c>
@@ -6947,7 +6953,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>27851</v>
       </c>
@@ -6967,7 +6973,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>27881</v>
       </c>
@@ -6987,7 +6993,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>27912</v>
       </c>
@@ -7007,7 +7013,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>27942</v>
       </c>
@@ -7027,7 +7033,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>27973</v>
       </c>
@@ -7047,7 +7053,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>28004</v>
       </c>
@@ -7067,7 +7073,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>28034</v>
       </c>
@@ -7087,7 +7093,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>28065</v>
       </c>
@@ -7107,7 +7113,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>28095</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>28126</v>
       </c>
@@ -7147,7 +7153,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>28157</v>
       </c>
@@ -7167,7 +7173,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>28185</v>
       </c>
@@ -7187,7 +7193,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>28216</v>
       </c>
@@ -7207,7 +7213,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>28246</v>
       </c>
@@ -7227,7 +7233,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>28277</v>
       </c>
@@ -7247,7 +7253,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>28307</v>
       </c>
@@ -7267,7 +7273,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>28338</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>28369</v>
       </c>
@@ -7307,7 +7313,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>28399</v>
       </c>
@@ -7327,7 +7333,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>28430</v>
       </c>
@@ -7347,7 +7353,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>28460</v>
       </c>
@@ -7367,7 +7373,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>28491</v>
       </c>
@@ -7387,7 +7393,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>28522</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>28550</v>
       </c>
@@ -7427,7 +7433,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>28581</v>
       </c>
@@ -7447,7 +7453,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>28611</v>
       </c>
@@ -7467,7 +7473,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>28642</v>
       </c>
@@ -7487,7 +7493,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>28672</v>
       </c>
@@ -7507,7 +7513,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>28703</v>
       </c>
@@ -7527,7 +7533,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>28734</v>
       </c>
@@ -7547,7 +7553,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>28764</v>
       </c>
@@ -7567,7 +7573,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>28795</v>
       </c>
@@ -7587,7 +7593,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>28825</v>
       </c>
@@ -7607,7 +7613,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>28856</v>
       </c>
@@ -7627,7 +7633,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>28887</v>
       </c>
@@ -7647,7 +7653,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>28915</v>
       </c>
@@ -7667,7 +7673,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>28946</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>28976</v>
       </c>
@@ -7707,7 +7713,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>29007</v>
       </c>
@@ -7727,7 +7733,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>29037</v>
       </c>
@@ -7747,7 +7753,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>29068</v>
       </c>
@@ -7767,7 +7773,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>29099</v>
       </c>
@@ -7787,7 +7793,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>29129</v>
       </c>
@@ -7807,7 +7813,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>29160</v>
       </c>
@@ -7827,7 +7833,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>29190</v>
       </c>
@@ -7847,7 +7853,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>29221</v>
       </c>
@@ -7867,7 +7873,7 @@
         <v>0.13300000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>29252</v>
       </c>
@@ -7887,7 +7893,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>29281</v>
       </c>
@@ -7907,7 +7913,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>29312</v>
       </c>
@@ -7927,7 +7933,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>29342</v>
       </c>
@@ -7947,7 +7953,7 @@
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>29373</v>
       </c>
@@ -7967,7 +7973,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>29403</v>
       </c>
@@ -7987,7 +7993,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>29434</v>
       </c>
@@ -8007,7 +8013,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>29465</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>29495</v>
       </c>
@@ -8047,7 +8053,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>29526</v>
       </c>
@@ -8067,7 +8073,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>29556</v>
       </c>
@@ -8087,7 +8093,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>29587</v>
       </c>
@@ -8107,7 +8113,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>29618</v>
       </c>
@@ -8127,7 +8133,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>29646</v>
       </c>
@@ -8147,7 +8153,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>29677</v>
       </c>
@@ -8167,7 +8173,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>29707</v>
       </c>
@@ -8187,7 +8193,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>29738</v>
       </c>
@@ -8207,7 +8213,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>29768</v>
       </c>
@@ -8227,7 +8233,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>29799</v>
       </c>
@@ -8247,7 +8253,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>29830</v>
       </c>
@@ -8267,7 +8273,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>29860</v>
       </c>
@@ -8287,7 +8293,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>29891</v>
       </c>
@@ -8307,7 +8313,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>29921</v>
       </c>
@@ -8327,7 +8333,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>29952</v>
       </c>
@@ -8347,7 +8353,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>29983</v>
       </c>
@@ -8367,7 +8373,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>30011</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>30042</v>
       </c>
@@ -8407,7 +8413,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>30072</v>
       </c>
@@ -8427,7 +8433,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>30103</v>
       </c>
@@ -8447,7 +8453,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>30133</v>
       </c>
@@ -8467,7 +8473,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>30164</v>
       </c>
@@ -8487,7 +8493,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>30195</v>
       </c>
@@ -8507,7 +8513,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>30225</v>
       </c>
@@ -8527,7 +8533,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>30256</v>
       </c>
@@ -8547,7 +8553,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>30286</v>
       </c>
@@ -8567,7 +8573,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>30317</v>
       </c>
@@ -8587,7 +8593,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>30348</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>30376</v>
       </c>
@@ -8627,7 +8633,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>30407</v>
       </c>
@@ -8647,7 +8653,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>30437</v>
       </c>
@@ -8667,7 +8673,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>30468</v>
       </c>
@@ -8687,7 +8693,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>30498</v>
       </c>
@@ -8707,7 +8713,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>30529</v>
       </c>
@@ -8727,7 +8733,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>30560</v>
       </c>
@@ -8747,7 +8753,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>30590</v>
       </c>
@@ -8767,7 +8773,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>30621</v>
       </c>
@@ -8787,7 +8793,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>30651</v>
       </c>
@@ -8807,7 +8813,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>30682</v>
       </c>
@@ -8827,7 +8833,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>30713</v>
       </c>
@@ -8847,7 +8853,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>30742</v>
       </c>
@@ -8867,7 +8873,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>30773</v>
       </c>
@@ -8887,7 +8893,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>30803</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>30834</v>
       </c>
@@ -8927,7 +8933,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>30864</v>
       </c>
@@ -8947,7 +8953,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>30895</v>
       </c>
@@ -8967,7 +8973,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>30926</v>
       </c>
@@ -8987,7 +8993,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>30956</v>
       </c>
@@ -9007,7 +9013,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>30987</v>
       </c>
@@ -9027,7 +9033,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>31017</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>31048</v>
       </c>
@@ -9067,7 +9073,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>31079</v>
       </c>
@@ -9087,7 +9093,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>31107</v>
       </c>
@@ -9107,7 +9113,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>31138</v>
       </c>
@@ -9127,7 +9133,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>31168</v>
       </c>
@@ -9147,7 +9153,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>31199</v>
       </c>
@@ -9167,7 +9173,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>31229</v>
       </c>
@@ -9187,7 +9193,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>31260</v>
       </c>
@@ -9207,7 +9213,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>31291</v>
       </c>
@@ -9227,7 +9233,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>31321</v>
       </c>
@@ -9247,7 +9253,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>31352</v>
       </c>
@@ -9267,7 +9273,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>31382</v>
       </c>
@@ -9287,7 +9293,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>31413</v>
       </c>
@@ -9307,7 +9313,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>31444</v>
       </c>
@@ -9327,7 +9333,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>31472</v>
       </c>
@@ -9347,7 +9353,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>31503</v>
       </c>
@@ -9367,7 +9373,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>31533</v>
       </c>
@@ -9387,7 +9393,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>31564</v>
       </c>
@@ -9407,7 +9413,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>31594</v>
       </c>
@@ -9427,7 +9433,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>31625</v>
       </c>
@@ -9447,7 +9453,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>31656</v>
       </c>
@@ -9467,7 +9473,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>31686</v>
       </c>
@@ -9487,7 +9493,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>31717</v>
       </c>
@@ -9507,7 +9513,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>31747</v>
       </c>
@@ -9527,7 +9533,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>31778</v>
       </c>
@@ -9547,7 +9553,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>31809</v>
       </c>
@@ -9567,7 +9573,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>31837</v>
       </c>
@@ -9587,7 +9593,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>31868</v>
       </c>
@@ -9607,7 +9613,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>31898</v>
       </c>
@@ -9627,7 +9633,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>31929</v>
       </c>
@@ -9647,7 +9653,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>31959</v>
       </c>
@@ -9667,7 +9673,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>31990</v>
       </c>
@@ -9687,7 +9693,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>32021</v>
       </c>
@@ -9707,7 +9713,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>32051</v>
       </c>
@@ -9727,7 +9733,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>32082</v>
       </c>
@@ -9747,7 +9753,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>32112</v>
       </c>
@@ -9767,7 +9773,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>32143</v>
       </c>
@@ -9787,7 +9793,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>32174</v>
       </c>
@@ -9807,7 +9813,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>32203</v>
       </c>
@@ -9827,7 +9833,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>32234</v>
       </c>
@@ -9847,7 +9853,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>32264</v>
       </c>
@@ -9867,7 +9873,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>32295</v>
       </c>
@@ -9887,7 +9893,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>32325</v>
       </c>
@@ -9907,7 +9913,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>32356</v>
       </c>
@@ -9927,7 +9933,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>32387</v>
       </c>
@@ -9947,7 +9953,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>32417</v>
       </c>
@@ -9967,7 +9973,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>32448</v>
       </c>
@@ -9987,7 +9993,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>32478</v>
       </c>
@@ -10007,7 +10013,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>32509</v>
       </c>
@@ -10027,7 +10033,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>32540</v>
       </c>
@@ -10047,7 +10053,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>32568</v>
       </c>
@@ -10067,7 +10073,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>32599</v>
       </c>
@@ -10087,7 +10093,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>32629</v>
       </c>
@@ -10107,7 +10113,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>32660</v>
       </c>
@@ -10127,7 +10133,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>32690</v>
       </c>
@@ -10147,7 +10153,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>32721</v>
       </c>
@@ -10167,7 +10173,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>32752</v>
       </c>
@@ -10187,7 +10193,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>32782</v>
       </c>
@@ -10207,7 +10213,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>32813</v>
       </c>
@@ -10227,7 +10233,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>32843</v>
       </c>
@@ -10247,7 +10253,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>32874</v>
       </c>
@@ -10267,7 +10273,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>32905</v>
       </c>
@@ -10287,7 +10293,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>32933</v>
       </c>
@@ -10307,7 +10313,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>32964</v>
       </c>
@@ -10327,7 +10333,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>32994</v>
       </c>
@@ -10347,7 +10353,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>33025</v>
       </c>
@@ -10367,7 +10373,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>33055</v>
       </c>
@@ -10387,7 +10393,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>33086</v>
       </c>
@@ -10407,7 +10413,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>33117</v>
       </c>
@@ -10427,7 +10433,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>33147</v>
       </c>
@@ -10447,7 +10453,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>33178</v>
       </c>
@@ -10467,7 +10473,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>33208</v>
       </c>
@@ -10487,7 +10493,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>33239</v>
       </c>
@@ -10507,7 +10513,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>33270</v>
       </c>
@@ -10527,7 +10533,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>33298</v>
       </c>
@@ -10547,7 +10553,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>33329</v>
       </c>
@@ -10567,7 +10573,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>33359</v>
       </c>
@@ -10587,7 +10593,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>33390</v>
       </c>
@@ -10607,7 +10613,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>33420</v>
       </c>
@@ -10627,7 +10633,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>33451</v>
       </c>
@@ -10647,7 +10653,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>33482</v>
       </c>
@@ -10667,7 +10673,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>33512</v>
       </c>
@@ -10687,7 +10693,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>33543</v>
       </c>
@@ -10707,7 +10713,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>33573</v>
       </c>
@@ -10727,7 +10733,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>33604</v>
       </c>
@@ -10747,7 +10753,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>33635</v>
       </c>
@@ -10767,7 +10773,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>33664</v>
       </c>
@@ -10787,7 +10793,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>33695</v>
       </c>
@@ -10807,7 +10813,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>33725</v>
       </c>
@@ -10827,7 +10833,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>33756</v>
       </c>
@@ -10847,7 +10853,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>33786</v>
       </c>
@@ -10867,7 +10873,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>33817</v>
       </c>
@@ -10887,7 +10893,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>33848</v>
       </c>
@@ -10907,7 +10913,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>33878</v>
       </c>
@@ -10927,7 +10933,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>33909</v>
       </c>
@@ -10947,7 +10953,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>33939</v>
       </c>
@@ -10967,7 +10973,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>33970</v>
       </c>
@@ -10987,7 +10993,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>34001</v>
       </c>
@@ -11007,7 +11013,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>34029</v>
       </c>
@@ -11027,7 +11033,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>34060</v>
       </c>
@@ -11047,7 +11053,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>34090</v>
       </c>
@@ -11067,7 +11073,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>34121</v>
       </c>
@@ -11087,7 +11093,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>34151</v>
       </c>
@@ -11107,7 +11113,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>34182</v>
       </c>
@@ -11127,7 +11133,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>34213</v>
       </c>
@@ -11147,7 +11153,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>34243</v>
       </c>
@@ -11167,7 +11173,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>34274</v>
       </c>
@@ -11187,7 +11193,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>34304</v>
       </c>
@@ -11207,7 +11213,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>34335</v>
       </c>
@@ -11227,7 +11233,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>34366</v>
       </c>
@@ -11247,7 +11253,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>34394</v>
       </c>
@@ -11267,7 +11273,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>34425</v>
       </c>
@@ -11287,7 +11293,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>34455</v>
       </c>
@@ -11307,7 +11313,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>34486</v>
       </c>
@@ -11327,7 +11333,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>34516</v>
       </c>
@@ -11347,7 +11353,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>34547</v>
       </c>
@@ -11367,7 +11373,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>34578</v>
       </c>
@@ -11387,7 +11393,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>34608</v>
       </c>
@@ -11407,7 +11413,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>34639</v>
       </c>
@@ -11427,7 +11433,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>34669</v>
       </c>
@@ -11447,7 +11453,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>34700</v>
       </c>
@@ -11467,7 +11473,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="6">
         <v>34731</v>
       </c>
@@ -11487,7 +11493,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="6">
         <v>34759</v>
       </c>
@@ -11507,7 +11513,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="6">
         <v>34790</v>
       </c>
@@ -11527,7 +11533,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="6">
         <v>34820</v>
       </c>
@@ -11547,7 +11553,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="6">
         <v>34851</v>
       </c>
@@ -11567,7 +11573,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="6">
         <v>34881</v>
       </c>
@@ -11587,7 +11593,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="6">
         <v>34912</v>
       </c>
@@ -11607,7 +11613,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="6">
         <v>34943</v>
       </c>
@@ -11627,7 +11633,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="6">
         <v>34973</v>
       </c>
@@ -11647,7 +11653,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="6">
         <v>35004</v>
       </c>
@@ -11667,7 +11673,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="6">
         <v>35034</v>
       </c>
@@ -11687,7 +11693,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="6">
         <v>35065</v>
       </c>
@@ -11707,7 +11713,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="6">
         <v>35096</v>
       </c>
@@ -11727,7 +11733,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="6">
         <v>35125</v>
       </c>
@@ -11747,7 +11753,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="6">
         <v>35156</v>
       </c>
@@ -11767,7 +11773,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="6">
         <v>35186</v>
       </c>
@@ -11787,7 +11793,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="6">
         <v>35217</v>
       </c>
@@ -11807,7 +11813,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="6">
         <v>35247</v>
       </c>
@@ -11827,7 +11833,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="6">
         <v>35278</v>
       </c>
@@ -11847,7 +11853,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="6">
         <v>35309</v>
       </c>
@@ -11867,7 +11873,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="6">
         <v>35339</v>
       </c>
@@ -11887,7 +11893,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="6">
         <v>35370</v>
       </c>
@@ -11907,7 +11913,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="6">
         <v>35400</v>
       </c>
@@ -11927,7 +11933,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="6">
         <v>35431</v>
       </c>
@@ -11947,7 +11953,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="6">
         <v>35462</v>
       </c>
@@ -11967,7 +11973,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="6">
         <v>35490</v>
       </c>
@@ -11987,7 +11993,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="6">
         <v>35521</v>
       </c>
@@ -12007,7 +12013,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="6">
         <v>35551</v>
       </c>
@@ -12027,7 +12033,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="6">
         <v>35582</v>
       </c>
@@ -12047,7 +12053,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="6">
         <v>35612</v>
       </c>
@@ -12067,7 +12073,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="6">
         <v>35643</v>
       </c>
@@ -12087,7 +12093,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="6">
         <v>35674</v>
       </c>
@@ -12107,7 +12113,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="6">
         <v>35704</v>
       </c>
@@ -12127,7 +12133,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="6">
         <v>35735</v>
       </c>
@@ -12147,7 +12153,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="6">
         <v>35765</v>
       </c>
@@ -12167,7 +12173,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="6">
         <v>35796</v>
       </c>
@@ -12187,7 +12193,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="6">
         <v>35827</v>
       </c>
@@ -12207,7 +12213,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="6">
         <v>35855</v>
       </c>
@@ -12227,7 +12233,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="6">
         <v>35886</v>
       </c>
@@ -12247,7 +12253,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="6">
         <v>35916</v>
       </c>
@@ -12267,7 +12273,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="6">
         <v>35947</v>
       </c>
@@ -12287,7 +12293,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="6">
         <v>35977</v>
       </c>
@@ -12307,7 +12313,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="6">
         <v>36008</v>
       </c>
@@ -12327,7 +12333,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="6">
         <v>36039</v>
       </c>
@@ -12347,7 +12353,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="6">
         <v>36069</v>
       </c>
@@ -12367,7 +12373,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="6">
         <v>36100</v>
       </c>
@@ -12387,7 +12393,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="6">
         <v>36130</v>
       </c>
@@ -12407,7 +12413,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="6">
         <v>36161</v>
       </c>
@@ -12427,7 +12433,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="6">
         <v>36192</v>
       </c>
@@ -12447,7 +12453,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="6">
         <v>36220</v>
       </c>
@@ -12467,7 +12473,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="6">
         <v>36251</v>
       </c>
@@ -12487,7 +12493,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="6">
         <v>36281</v>
       </c>
@@ -12507,7 +12513,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="6">
         <v>36312</v>
       </c>
@@ -12527,7 +12533,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="6">
         <v>36342</v>
       </c>
@@ -12547,7 +12553,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="6">
         <v>36373</v>
       </c>
@@ -12567,7 +12573,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="6">
         <v>36404</v>
       </c>
@@ -12587,7 +12593,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="6">
         <v>36434</v>
       </c>
@@ -12607,7 +12613,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="6">
         <v>36465</v>
       </c>
@@ -12627,7 +12633,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="6">
         <v>36495</v>
       </c>
@@ -12647,7 +12653,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="6">
         <v>36526</v>
       </c>
@@ -12667,7 +12673,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="6">
         <v>36557</v>
       </c>
@@ -12687,7 +12693,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="6">
         <v>36586</v>
       </c>
@@ -12707,7 +12713,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="6">
         <v>36617</v>
       </c>
@@ -12727,7 +12733,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="6">
         <v>36647</v>
       </c>
@@ -12747,7 +12753,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="6">
         <v>36678</v>
       </c>
@@ -12767,7 +12773,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="6">
         <v>36708</v>
       </c>
@@ -12787,7 +12793,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="6">
         <v>36739</v>
       </c>
@@ -12807,7 +12813,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="6">
         <v>36770</v>
       </c>
@@ -12827,7 +12833,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="6">
         <v>36800</v>
       </c>
@@ -12847,7 +12853,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="6">
         <v>36831</v>
       </c>
@@ -12867,7 +12873,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="6">
         <v>36861</v>
       </c>
@@ -12887,7 +12893,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="6">
         <v>36892</v>
       </c>
@@ -12907,7 +12913,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="6">
         <v>36923</v>
       </c>
@@ -12927,7 +12933,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="6">
         <v>36951</v>
       </c>
@@ -12947,7 +12953,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="6">
         <v>36982</v>
       </c>
@@ -12967,7 +12973,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="6">
         <v>37012</v>
       </c>
@@ -12987,7 +12993,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="6">
         <v>37043</v>
       </c>
@@ -13007,7 +13013,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="6">
         <v>37073</v>
       </c>
@@ -13027,7 +13033,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="6">
         <v>37104</v>
       </c>
@@ -13047,7 +13053,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="6">
         <v>37135</v>
       </c>
@@ -13067,7 +13073,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="6">
         <v>37165</v>
       </c>
@@ -13087,7 +13093,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="6">
         <v>37196</v>
       </c>
@@ -13107,7 +13113,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="6">
         <v>37226</v>
       </c>
@@ -13127,7 +13133,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="6">
         <v>37257</v>
       </c>
@@ -13147,7 +13153,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="6">
         <v>37288</v>
       </c>
@@ -13167,7 +13173,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="6">
         <v>37316</v>
       </c>
@@ -13187,7 +13193,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="6">
         <v>37347</v>
       </c>
@@ -13207,7 +13213,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="6">
         <v>37377</v>
       </c>
@@ -13227,7 +13233,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="6">
         <v>37408</v>
       </c>
@@ -13247,7 +13253,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="6">
         <v>37438</v>
       </c>
@@ -13267,7 +13273,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="6">
         <v>37469</v>
       </c>
@@ -13287,7 +13293,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="6">
         <v>37500</v>
       </c>
@@ -13307,7 +13313,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="6">
         <v>37530</v>
       </c>
@@ -13327,7 +13333,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="6">
         <v>37561</v>
       </c>
@@ -13347,7 +13353,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="6">
         <v>37591</v>
       </c>
@@ -13367,7 +13373,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="6">
         <v>37622</v>
       </c>
@@ -13387,7 +13393,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="6">
         <v>37653</v>
       </c>
@@ -13407,7 +13413,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="6">
         <v>37681</v>
       </c>
@@ -13427,7 +13433,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="6">
         <v>37712</v>
       </c>
@@ -13447,7 +13453,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="6">
         <v>37742</v>
       </c>
@@ -13467,7 +13473,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="6">
         <v>37773</v>
       </c>
@@ -13487,7 +13493,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="6">
         <v>37803</v>
       </c>
@@ -13507,7 +13513,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="6">
         <v>37834</v>
       </c>
@@ -13527,7 +13533,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="6">
         <v>37865</v>
       </c>
@@ -13547,7 +13553,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="6">
         <v>37895</v>
       </c>
@@ -13567,7 +13573,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="6">
         <v>37926</v>
       </c>
@@ -13587,7 +13593,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="6">
         <v>37956</v>
       </c>
@@ -13607,7 +13613,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="6">
         <v>37987</v>
       </c>
@@ -13627,7 +13633,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="6">
         <v>38018</v>
       </c>
@@ -13647,7 +13653,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="6">
         <v>38047</v>
       </c>
@@ -13667,7 +13673,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="6">
         <v>38078</v>
       </c>
@@ -13687,7 +13693,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="6">
         <v>38108</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="6">
         <v>38139</v>
       </c>
@@ -13727,7 +13733,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="6">
         <v>38169</v>
       </c>
@@ -13747,7 +13753,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="6">
         <v>38200</v>
       </c>
@@ -13767,7 +13773,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="6">
         <v>38231</v>
       </c>
@@ -13787,7 +13793,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="6">
         <v>38261</v>
       </c>
@@ -13807,7 +13813,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="6">
         <v>38292</v>
       </c>
@@ -13827,7 +13833,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="6">
         <v>38322</v>
       </c>
@@ -13847,7 +13853,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="6">
         <v>38353</v>
       </c>
@@ -13867,7 +13873,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="6">
         <v>38384</v>
       </c>
@@ -13887,7 +13893,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="6">
         <v>38412</v>
       </c>
@@ -13907,7 +13913,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="6">
         <v>38443</v>
       </c>
@@ -13927,7 +13933,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="6">
         <v>38473</v>
       </c>
@@ -13947,7 +13953,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="6">
         <v>38504</v>
       </c>
@@ -13967,7 +13973,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="6">
         <v>38534</v>
       </c>
@@ -13987,7 +13993,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="6">
         <v>38565</v>
       </c>
@@ -14007,7 +14013,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="6">
         <v>38596</v>
       </c>
@@ -14027,7 +14033,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="6">
         <v>38626</v>
       </c>
@@ -14047,7 +14053,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="6">
         <v>38657</v>
       </c>
@@ -14067,7 +14073,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="6">
         <v>38687</v>
       </c>
@@ -14087,7 +14093,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="6">
         <v>38718</v>
       </c>
@@ -14107,7 +14113,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="6">
         <v>38749</v>
       </c>
@@ -14127,7 +14133,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="6">
         <v>38777</v>
       </c>
@@ -14147,7 +14153,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="6">
         <v>38808</v>
       </c>
@@ -14167,7 +14173,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="6">
         <v>38838</v>
       </c>
@@ -14187,7 +14193,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="6">
         <v>38869</v>
       </c>
@@ -14207,7 +14213,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="6">
         <v>38899</v>
       </c>
@@ -14227,7 +14233,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="6">
         <v>38930</v>
       </c>
@@ -14247,7 +14253,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="6">
         <v>38961</v>
       </c>
@@ -14267,7 +14273,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="6">
         <v>38991</v>
       </c>
@@ -14287,7 +14293,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="6">
         <v>39022</v>
       </c>
@@ -14307,7 +14313,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="6">
         <v>39052</v>
       </c>
@@ -14327,7 +14333,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="6">
         <v>39083</v>
       </c>
@@ -14347,7 +14353,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="6">
         <v>39114</v>
       </c>
@@ -14367,7 +14373,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="6">
         <v>39142</v>
       </c>
@@ -14387,7 +14393,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="6">
         <v>39173</v>
       </c>
@@ -14407,7 +14413,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="6">
         <v>39203</v>
       </c>
@@ -14427,7 +14433,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="6">
         <v>39234</v>
       </c>
@@ -14447,7 +14453,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="6">
         <v>39264</v>
       </c>
@@ -14467,7 +14473,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="6">
         <v>39295</v>
       </c>
@@ -14487,7 +14493,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="6">
         <v>39326</v>
       </c>
@@ -14507,7 +14513,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="6">
         <v>39356</v>
       </c>
@@ -14527,7 +14533,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="6">
         <v>39387</v>
       </c>
@@ -14547,7 +14553,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="6">
         <v>39417</v>
       </c>
@@ -14567,7 +14573,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="6">
         <v>39448</v>
       </c>
@@ -14587,7 +14593,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="6">
         <v>39479</v>
       </c>
@@ -14607,7 +14613,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="6">
         <v>39508</v>
       </c>
@@ -14627,7 +14633,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="6">
         <v>39539</v>
       </c>
@@ -14647,7 +14653,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="6">
         <v>39569</v>
       </c>
@@ -14667,7 +14673,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="6">
         <v>39600</v>
       </c>
@@ -14687,7 +14693,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="6">
         <v>39630</v>
       </c>
@@ -14707,7 +14713,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="6">
         <v>39661</v>
       </c>
@@ -14727,7 +14733,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="6">
         <v>39692</v>
       </c>
@@ -14747,7 +14753,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="6">
         <v>39722</v>
       </c>
@@ -14767,7 +14773,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="6">
         <v>39753</v>
       </c>
@@ -14787,7 +14793,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="6">
         <v>39783</v>
       </c>
@@ -14807,7 +14813,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="6">
         <v>39814</v>
       </c>
@@ -14827,7 +14833,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="6">
         <v>39845</v>
       </c>
@@ -14847,7 +14853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="6">
         <v>39873</v>
       </c>
@@ -14867,7 +14873,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="6">
         <v>39904</v>
       </c>
@@ -14887,7 +14893,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="6">
         <v>39934</v>
       </c>
@@ -14907,7 +14913,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="6">
         <v>39965</v>
       </c>
@@ -14927,7 +14933,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="6">
         <v>39995</v>
       </c>
@@ -14947,7 +14953,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="6">
         <v>40026</v>
       </c>
@@ -14967,7 +14973,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="6">
         <v>40057</v>
       </c>
@@ -14987,7 +14993,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="6">
         <v>40087</v>
       </c>
@@ -15007,7 +15013,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="6">
         <v>40118</v>
       </c>
@@ -15027,7 +15033,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="6">
         <v>40148</v>
       </c>
@@ -15047,7 +15053,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="6">
         <v>40179</v>
       </c>
@@ -15067,7 +15073,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="6">
         <v>40210</v>
       </c>
@@ -15087,7 +15093,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="6">
         <v>40238</v>
       </c>
@@ -15107,7 +15113,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="6">
         <v>40269</v>
       </c>
@@ -15127,7 +15133,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="6">
         <v>40299</v>
       </c>
@@ -15147,7 +15153,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="6">
         <v>40330</v>
       </c>
@@ -15167,7 +15173,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="6">
         <v>40360</v>
       </c>
@@ -15187,7 +15193,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="6">
         <v>40391</v>
       </c>
@@ -15207,7 +15213,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="6">
         <v>40422</v>
       </c>
@@ -15227,7 +15233,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="6">
         <v>40452</v>
       </c>
@@ -15247,7 +15253,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="6">
         <v>40483</v>
       </c>
@@ -15267,7 +15273,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="6">
         <v>40513</v>
       </c>
@@ -15287,7 +15293,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="6">
         <v>40544</v>
       </c>
@@ -15307,7 +15313,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="6">
         <v>40575</v>
       </c>
@@ -15327,7 +15333,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="6">
         <v>40603</v>
       </c>
@@ -15347,7 +15353,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="6">
         <v>40634</v>
       </c>
@@ -15367,7 +15373,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="6">
         <v>40664</v>
       </c>
@@ -15387,7 +15393,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="6">
         <v>40695</v>
       </c>
@@ -15407,7 +15413,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="6">
         <v>40725</v>
       </c>
@@ -15427,7 +15433,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="6">
         <v>40756</v>
       </c>
@@ -15447,7 +15453,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="6">
         <v>40787</v>
       </c>
@@ -15467,7 +15473,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="6">
         <v>40817</v>
       </c>
@@ -15487,7 +15493,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="6">
         <v>40848</v>
       </c>
@@ -15507,7 +15513,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="6">
         <v>40878</v>
       </c>
@@ -15527,7 +15533,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="6">
         <v>40909</v>
       </c>
@@ -15547,7 +15553,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="6">
         <v>40940</v>
       </c>
@@ -15567,7 +15573,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="6">
         <v>40969</v>
       </c>
@@ -15587,7 +15593,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="6">
         <v>41000</v>
       </c>
@@ -15610,7 +15616,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="6">
         <v>41030</v>
       </c>
@@ -15633,7 +15639,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="6">
         <v>41061</v>
       </c>
@@ -15656,7 +15662,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="6">
         <v>41091</v>
       </c>
@@ -15679,7 +15685,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="6">
         <v>41122</v>
       </c>
@@ -15702,7 +15708,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="6">
         <v>41153</v>
       </c>
@@ -15725,7 +15731,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="6">
         <v>41183</v>
       </c>
@@ -15748,7 +15754,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="6">
         <v>41214</v>
       </c>
@@ -15771,7 +15777,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="6">
         <v>41244</v>
       </c>
@@ -15794,7 +15800,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="6">
         <v>41275</v>
       </c>
@@ -15817,7 +15823,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="6">
         <v>41306</v>
       </c>
@@ -15840,7 +15846,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="6">
         <v>41334</v>
       </c>
@@ -15863,7 +15869,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="6">
         <v>41365</v>
       </c>
@@ -15886,7 +15892,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="6">
         <v>41395</v>
       </c>
@@ -15909,7 +15915,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="6">
         <v>41426</v>
       </c>
@@ -15932,7 +15938,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="6">
         <v>41456</v>
       </c>
@@ -15955,7 +15961,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="6">
         <v>41487</v>
       </c>
@@ -15978,7 +15984,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="6">
         <v>41518</v>
       </c>
@@ -16001,7 +16007,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="6">
         <v>41548</v>
       </c>
@@ -16024,7 +16030,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="6">
         <v>41579</v>
       </c>
@@ -16047,7 +16053,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="6">
         <v>41609</v>
       </c>
@@ -16070,7 +16076,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="6">
         <v>41640</v>
       </c>
@@ -16093,7 +16099,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="6">
         <v>41671</v>
       </c>
@@ -16116,7 +16122,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="6">
         <v>41699</v>
       </c>
@@ -16139,7 +16145,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="6">
         <v>41730</v>
       </c>
@@ -16162,7 +16168,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A535" s="6">
         <v>41760</v>
       </c>
@@ -16185,7 +16191,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A536" s="6">
         <v>41791</v>
       </c>
@@ -16208,7 +16214,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A537" s="6">
         <v>41821</v>
       </c>
@@ -16231,7 +16237,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A538" s="6">
         <v>41852</v>
       </c>
@@ -16254,7 +16260,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A539" s="6">
         <v>41883</v>
       </c>
@@ -16277,7 +16283,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A540" s="6">
         <v>41913</v>
       </c>
@@ -16300,7 +16306,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A541" s="6">
         <v>41944</v>
       </c>
@@ -16323,7 +16329,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A542" s="6">
         <v>41974</v>
       </c>
@@ -16346,7 +16352,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A543" s="6">
         <v>42005</v>
       </c>
@@ -16369,7 +16375,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A544" s="6">
         <v>42036</v>
       </c>
@@ -16392,7 +16398,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A545" s="6">
         <v>42064</v>
       </c>
@@ -16415,7 +16421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A546" s="6">
         <v>42095</v>
       </c>
@@ -16438,7 +16444,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A547" s="6">
         <v>42125</v>
       </c>
@@ -16461,7 +16467,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A548" s="6">
         <v>42156</v>
       </c>
@@ -16484,7 +16490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A549" s="6">
         <v>42186</v>
       </c>
@@ -16507,7 +16513,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A550" s="6">
         <v>42217</v>
       </c>
@@ -16530,7 +16536,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A551" s="6">
         <v>42248</v>
       </c>
@@ -16553,7 +16559,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A552" s="6">
         <v>42278</v>
       </c>
@@ -16576,7 +16582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A553" s="6">
         <v>42309</v>
       </c>
@@ -16599,7 +16605,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A554" s="6">
         <v>42339</v>
       </c>
@@ -16622,7 +16628,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A555" s="6">
         <v>42370</v>
       </c>
@@ -16645,7 +16651,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A556" s="6">
         <v>42401</v>
       </c>
@@ -16668,7 +16674,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A557" s="6">
         <v>42430</v>
       </c>
@@ -16691,7 +16697,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A558" s="6">
         <v>42461</v>
       </c>
@@ -16714,7 +16720,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A559" s="6">
         <v>42491</v>
       </c>
@@ -16737,7 +16743,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A560" s="6">
         <v>42522</v>
       </c>
@@ -16760,7 +16766,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A561" s="6">
         <v>42552</v>
       </c>
@@ -16783,7 +16789,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A562" s="6">
         <v>42583</v>
       </c>
@@ -16806,7 +16812,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A563" s="6">
         <v>42614</v>
       </c>
@@ -16829,7 +16835,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A564" s="6">
         <v>42644</v>
       </c>
@@ -16852,7 +16858,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A565" s="6">
         <v>42675</v>
       </c>
@@ -16875,7 +16881,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A566" s="6">
         <v>42705</v>
       </c>
@@ -16898,7 +16904,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A567" s="6">
         <v>42736</v>
       </c>
@@ -16921,7 +16927,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A568" s="6">
         <v>42767</v>
       </c>
@@ -16944,7 +16950,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A569" s="6">
         <v>42795</v>
       </c>
@@ -16967,7 +16973,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A570" s="6">
         <v>42826</v>
       </c>
@@ -16990,7 +16996,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A571" s="6">
         <v>42856</v>
       </c>
@@ -17013,7 +17019,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A572" s="6">
         <v>42887</v>
       </c>
@@ -17036,7 +17042,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A573" s="6">
         <v>42917</v>
       </c>
@@ -17059,7 +17065,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A574" s="6">
         <v>42948</v>
       </c>
@@ -17082,7 +17088,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A575" s="6">
         <v>42979</v>
       </c>
@@ -17105,7 +17111,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A576" s="6">
         <v>43009</v>
       </c>
@@ -17128,7 +17134,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A577" s="6">
         <v>43040</v>
       </c>
@@ -17151,7 +17157,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A578" s="6">
         <v>43070</v>
       </c>
@@ -17174,7 +17180,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A579" s="6">
         <v>43101</v>
       </c>
@@ -17197,7 +17203,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A580" s="6">
         <v>43132</v>
       </c>
@@ -17220,7 +17226,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A581" s="6">
         <v>43160</v>
       </c>
@@ -17243,7 +17249,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A582" s="6">
         <v>43191</v>
       </c>
@@ -17266,7 +17272,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A583" s="6">
         <v>43221</v>
       </c>
@@ -17289,7 +17295,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A584" s="6">
         <v>43252</v>
       </c>
@@ -17312,7 +17318,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A585" s="6">
         <v>43282</v>
       </c>
@@ -17335,7 +17341,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A586" s="6">
         <v>43313</v>
       </c>
@@ -17358,7 +17364,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A587" s="6">
         <v>43344</v>
       </c>
@@ -17381,7 +17387,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A588" s="6">
         <v>43374</v>
       </c>
@@ -17404,7 +17410,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A589" s="6">
         <v>43405</v>
       </c>
@@ -17427,7 +17433,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A590" s="6">
         <v>43435</v>
       </c>
@@ -17450,7 +17456,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A591" s="6">
         <v>43466</v>
       </c>
@@ -17473,7 +17479,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A592" s="6">
         <v>43497</v>
       </c>
@@ -17496,7 +17502,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A593" s="6">
         <v>43525</v>
       </c>
@@ -17519,7 +17525,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A594" s="6">
         <v>43556</v>
       </c>
@@ -17542,7 +17548,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A595" s="6">
         <v>43586</v>
       </c>
@@ -17565,7 +17571,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A596" s="6">
         <v>43617</v>
       </c>
@@ -17588,7 +17594,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A597" s="6">
         <v>43647</v>
       </c>
@@ -17611,7 +17617,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A598" s="6">
         <v>43678</v>
       </c>
@@ -17634,7 +17640,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A599" s="6">
         <v>43709</v>
       </c>
@@ -17657,7 +17663,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A600" s="6">
         <v>43739</v>
       </c>
@@ -17680,7 +17686,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A601" s="6">
         <v>43770</v>
       </c>
@@ -17703,7 +17709,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A602" s="6">
         <v>43800</v>
       </c>
@@ -17726,7 +17732,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A603" s="6">
         <v>43831</v>
       </c>
@@ -17749,7 +17755,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A604" s="6">
         <v>43862</v>
       </c>
@@ -17772,7 +17778,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A605" s="6">
         <v>43891</v>
       </c>
@@ -17795,7 +17801,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A606" s="6">
         <v>43922</v>
       </c>
@@ -17818,7 +17824,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A607" s="6">
         <v>43952</v>
       </c>
@@ -17841,7 +17847,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A608" s="6">
         <v>43983</v>
       </c>
@@ -17864,7 +17870,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A609" s="6">
         <v>44013</v>
       </c>
@@ -17887,7 +17893,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A610" s="6">
         <v>44044</v>
       </c>
@@ -17910,7 +17916,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A611" s="6">
         <v>44075</v>
       </c>
@@ -17933,7 +17939,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A612" s="6">
         <v>44105</v>
       </c>
@@ -17956,7 +17962,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A613" s="6">
         <v>44136</v>
       </c>
@@ -17979,7 +17985,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A614" s="6">
         <v>44166</v>
       </c>
@@ -18002,7 +18008,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A615" s="6">
         <v>44197</v>
       </c>
@@ -18025,7 +18031,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A616" s="6">
         <v>44228</v>
       </c>
@@ -18048,7 +18054,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A617" s="6">
         <v>44256</v>
       </c>
@@ -18071,7 +18077,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A618" s="6">
         <v>44287</v>
       </c>
@@ -18094,7 +18100,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A619" s="6">
         <v>44317</v>
       </c>
@@ -18117,7 +18123,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A620" s="6">
         <v>44348</v>
       </c>
@@ -18140,7 +18146,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A621" s="6">
         <v>44378</v>
       </c>
@@ -18163,7 +18169,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A622" s="6">
         <v>44409</v>
       </c>
@@ -18186,7 +18192,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A623" s="6">
         <v>44440</v>
       </c>
@@ -18209,7 +18215,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A624" s="6">
         <v>44470</v>
       </c>
@@ -18232,7 +18238,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A625" s="6">
         <v>44501</v>
       </c>
@@ -18255,7 +18261,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A626" s="6">
         <v>44531</v>
       </c>
@@ -18278,7 +18284,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A627" s="6">
         <v>44562</v>
       </c>
@@ -18301,7 +18307,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A628" s="6">
         <v>44593</v>
       </c>
@@ -18324,7 +18330,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A629" s="6">
         <v>44621</v>
       </c>
@@ -18347,7 +18353,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A630" s="6">
         <v>44652</v>
       </c>
@@ -18370,7 +18376,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A631" s="6">
         <v>44682</v>
       </c>
@@ -18393,7 +18399,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A632" s="6">
         <v>44713</v>
       </c>
@@ -18416,7 +18422,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A633" s="6">
         <v>44743</v>
       </c>
@@ -18439,7 +18445,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A634" s="6">
         <v>44774</v>
       </c>
@@ -18462,7 +18468,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A635" s="6">
         <v>44805</v>
       </c>
@@ -18485,7 +18491,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A636" s="6">
         <v>44835</v>
       </c>
@@ -18508,7 +18514,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A637" s="6">
         <v>44866</v>
       </c>
@@ -18531,7 +18537,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A638" s="6">
         <v>44896</v>
       </c>
@@ -18554,7 +18560,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A639" s="6">
         <v>44927</v>
       </c>
@@ -18577,7 +18583,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A640" s="6">
         <v>44958</v>
       </c>
@@ -18600,7 +18606,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A641" s="6">
         <v>44986</v>
       </c>
@@ -18623,7 +18629,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A642" s="6">
         <v>45017</v>
       </c>
@@ -18646,7 +18652,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A643" s="6">
         <v>45047</v>
       </c>
@@ -18669,7 +18675,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A644" s="6">
         <v>45078</v>
       </c>
@@ -18692,7 +18698,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A645" s="6">
         <v>45108</v>
       </c>
@@ -18715,7 +18721,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A646" s="6">
         <v>45139</v>
       </c>
@@ -18738,7 +18744,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A647" s="6">
         <v>45170</v>
       </c>
@@ -18761,7 +18767,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A648" s="6">
         <v>45200</v>
       </c>
@@ -18784,7 +18790,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A649" s="6">
         <v>45231</v>
       </c>
@@ -18807,7 +18813,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A650" s="6">
         <v>45261</v>
       </c>
@@ -18830,7 +18836,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A651" s="6">
         <v>45292</v>
       </c>
@@ -18853,7 +18859,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A652" s="6">
         <v>45323</v>
       </c>
@@ -18876,7 +18882,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A653" s="6">
         <v>45352</v>
       </c>
@@ -18899,7 +18905,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A654" s="6">
         <v>45383</v>
       </c>
@@ -18922,7 +18928,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A655" s="6">
         <v>45413</v>
       </c>
@@ -18945,7 +18951,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A656" s="6">
         <v>45444</v>
       </c>
@@ -18968,7 +18974,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A657" s="6">
         <v>45474</v>
       </c>
@@ -18991,7 +18997,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A658" s="6">
         <v>45505</v>
       </c>
@@ -19014,7 +19020,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A659" s="6">
         <v>45536</v>
       </c>
@@ -19037,7 +19043,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A660" s="6">
         <v>45566</v>
       </c>
@@ -19060,7 +19066,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A661" s="6">
         <v>45597</v>
       </c>
@@ -19083,7 +19089,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A662" s="6">
         <v>45627</v>
       </c>
@@ -19106,7 +19112,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A663" s="6">
         <v>45658</v>
       </c>
@@ -19129,7 +19135,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A664" s="6">
         <v>45689</v>
       </c>
@@ -19152,7 +19158,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A665" s="6">
         <v>45717</v>
       </c>
@@ -19175,7 +19181,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A666" s="6">
         <v>45748</v>
       </c>
@@ -19198,7 +19204,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A667" s="6">
         <v>45778</v>
       </c>
@@ -19221,7 +19227,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A668" s="6">
         <v>45809</v>
       </c>
@@ -19244,7 +19250,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A669" s="6">
         <v>45839</v>
       </c>
@@ -19267,7 +19273,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A670" s="6">
         <v>45870</v>
       </c>
@@ -19290,7 +19296,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A671" s="6">
         <v>45901</v>
       </c>
@@ -19313,7 +19319,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A672" s="6">
         <v>45962</v>
       </c>
@@ -19336,7 +19342,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A673" s="6">
         <v>45992</v>
       </c>
@@ -19359,7 +19365,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A674" s="6">
         <v>46023</v>
       </c>
@@ -19382,7 +19388,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A675" s="6">
         <v>46054</v>
       </c>
@@ -19402,6 +19408,29 @@
         <v>2.4E-2</v>
       </c>
       <c r="G675" s="9">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A676" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B676" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C676" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D676" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E676" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F676" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G676" s="9">
         <v>2.4E-2</v>
       </c>
     </row>
@@ -19415,7 +19444,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EBF4DF-B181-4399-AF18-DD9803B9FC52}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/macro/USA/USCPI YoY.xlsx
+++ b/data/macro/USA/USCPI YoY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4DC65F-2957-4E0B-AADD-77FC3F33EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F495F355-E5DE-4EA3-901A-40DEF461775A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{048C2A35-BEFE-40E9-9968-E0CB19CCA872}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="9">
   <si>
     <t>Release Date</t>
   </si>
@@ -233,9 +233,8 @@
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -252,17 +251,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="15875">
+            <a:ln w="15875" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:numRef>
               <c:f>data!$B$2:$B$1675</c:f>
@@ -2293,6 +2292,9 @@
                 </c:pt>
                 <c:pt idx="674">
                   <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>46154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4328,9 +4330,13 @@
                 <c:pt idx="674">
                   <c:v>3.3000000000000002E-2</c:v>
                 </c:pt>
+                <c:pt idx="675">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-393D-4C96-A35C-A8EA38DA8486}"/>
@@ -4345,10 +4351,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:smooth val="0"/>
         <c:axId val="1775995792"/>
         <c:axId val="1172243136"/>
-      </c:barChart>
+      </c:lineChart>
       <c:dateAx>
         <c:axId val="1775995792"/>
         <c:scaling>
@@ -5402,7 +5408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DCC3F54-AD1C-4CCF-B8C0-3F784AA58BEE}">
-  <dimension ref="A1:G676"/>
+  <dimension ref="A1:G677"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -5436,7 +5442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>25538</v>
       </c>
@@ -5453,7 +5459,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>25569</v>
       </c>
@@ -5473,7 +5479,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>25600</v>
       </c>
@@ -5493,7 +5499,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>25628</v>
       </c>
@@ -5513,7 +5519,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>25659</v>
       </c>
@@ -5533,7 +5539,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>25689</v>
       </c>
@@ -5553,7 +5559,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>25720</v>
       </c>
@@ -5573,7 +5579,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>25750</v>
       </c>
@@ -5593,7 +5599,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>25781</v>
       </c>
@@ -5613,7 +5619,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25812</v>
       </c>
@@ -5633,7 +5639,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>25842</v>
       </c>
@@ -5653,7 +5659,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>25873</v>
       </c>
@@ -5673,7 +5679,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>25903</v>
       </c>
@@ -5693,7 +5699,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>25934</v>
       </c>
@@ -5713,7 +5719,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>25965</v>
       </c>
@@ -5733,7 +5739,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>25993</v>
       </c>
@@ -5753,7 +5759,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>26024</v>
       </c>
@@ -5773,7 +5779,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>26054</v>
       </c>
@@ -5793,7 +5799,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>26085</v>
       </c>
@@ -5813,7 +5819,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>26115</v>
       </c>
@@ -5833,7 +5839,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>26146</v>
       </c>
@@ -5853,7 +5859,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>26177</v>
       </c>
@@ -5873,7 +5879,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>26207</v>
       </c>
@@ -5893,7 +5899,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>26238</v>
       </c>
@@ -5913,7 +5919,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26268</v>
       </c>
@@ -5933,7 +5939,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>26299</v>
       </c>
@@ -5953,7 +5959,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>26330</v>
       </c>
@@ -5973,7 +5979,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>26359</v>
       </c>
@@ -5993,7 +5999,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>26390</v>
       </c>
@@ -6013,7 +6019,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>26420</v>
       </c>
@@ -6033,7 +6039,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>26451</v>
       </c>
@@ -6053,7 +6059,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>26481</v>
       </c>
@@ -6073,7 +6079,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>26512</v>
       </c>
@@ -6093,7 +6099,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>26543</v>
       </c>
@@ -6113,7 +6119,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>26573</v>
       </c>
@@ -6133,7 +6139,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>26604</v>
       </c>
@@ -6153,7 +6159,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>26634</v>
       </c>
@@ -6173,7 +6179,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>26665</v>
       </c>
@@ -6193,7 +6199,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>26696</v>
       </c>
@@ -6213,7 +6219,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>26724</v>
       </c>
@@ -6233,7 +6239,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>26755</v>
       </c>
@@ -6253,7 +6259,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>26785</v>
       </c>
@@ -6273,7 +6279,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>26816</v>
       </c>
@@ -6293,7 +6299,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>26846</v>
       </c>
@@ -6313,7 +6319,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>26877</v>
       </c>
@@ -6333,7 +6339,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>26908</v>
       </c>
@@ -6353,7 +6359,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>26938</v>
       </c>
@@ -6373,7 +6379,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>26969</v>
       </c>
@@ -6393,7 +6399,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>26999</v>
       </c>
@@ -6413,7 +6419,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>27030</v>
       </c>
@@ -6433,7 +6439,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>27061</v>
       </c>
@@ -6453,7 +6459,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>27089</v>
       </c>
@@ -6473,7 +6479,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>27120</v>
       </c>
@@ -6493,7 +6499,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>27150</v>
       </c>
@@ -6513,7 +6519,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>27181</v>
       </c>
@@ -6533,7 +6539,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>27211</v>
       </c>
@@ -6553,7 +6559,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>27242</v>
       </c>
@@ -6573,7 +6579,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>27273</v>
       </c>
@@ -6593,7 +6599,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>27303</v>
       </c>
@@ -6613,7 +6619,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>27334</v>
       </c>
@@ -6633,7 +6639,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>27364</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>27395</v>
       </c>
@@ -6673,7 +6679,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>27426</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>27454</v>
       </c>
@@ -6713,7 +6719,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>27485</v>
       </c>
@@ -6733,7 +6739,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>27515</v>
       </c>
@@ -6753,7 +6759,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>27546</v>
       </c>
@@ -6773,7 +6779,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>27576</v>
       </c>
@@ -6793,7 +6799,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>27607</v>
       </c>
@@ -6813,7 +6819,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>27638</v>
       </c>
@@ -6833,7 +6839,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>27668</v>
       </c>
@@ -6853,7 +6859,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>27699</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>27729</v>
       </c>
@@ -6893,7 +6899,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>27760</v>
       </c>
@@ -6913,7 +6919,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>27791</v>
       </c>
@@ -6933,7 +6939,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>27820</v>
       </c>
@@ -6953,7 +6959,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>27851</v>
       </c>
@@ -6973,7 +6979,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>27881</v>
       </c>
@@ -6993,7 +6999,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>27912</v>
       </c>
@@ -7013,7 +7019,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>27942</v>
       </c>
@@ -7033,7 +7039,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>27973</v>
       </c>
@@ -7053,7 +7059,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>28004</v>
       </c>
@@ -7073,7 +7079,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>28034</v>
       </c>
@@ -7093,7 +7099,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>28065</v>
       </c>
@@ -7113,7 +7119,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>28095</v>
       </c>
@@ -7133,7 +7139,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>28126</v>
       </c>
@@ -7153,7 +7159,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>28157</v>
       </c>
@@ -7173,7 +7179,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>28185</v>
       </c>
@@ -7193,7 +7199,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>28216</v>
       </c>
@@ -7213,7 +7219,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>28246</v>
       </c>
@@ -7233,7 +7239,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>28277</v>
       </c>
@@ -7253,7 +7259,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>28307</v>
       </c>
@@ -7273,7 +7279,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>28338</v>
       </c>
@@ -7293,7 +7299,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>28369</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>28399</v>
       </c>
@@ -7333,7 +7339,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>28430</v>
       </c>
@@ -7353,7 +7359,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>28460</v>
       </c>
@@ -7373,7 +7379,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>28491</v>
       </c>
@@ -7393,7 +7399,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>28522</v>
       </c>
@@ -7413,7 +7419,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>28550</v>
       </c>
@@ -7433,7 +7439,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>28581</v>
       </c>
@@ -7453,7 +7459,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>28611</v>
       </c>
@@ -7473,7 +7479,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>28642</v>
       </c>
@@ -7493,7 +7499,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>28672</v>
       </c>
@@ -7513,7 +7519,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>28703</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>28734</v>
       </c>
@@ -7553,7 +7559,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>28764</v>
       </c>
@@ -7573,7 +7579,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>28795</v>
       </c>
@@ -7593,7 +7599,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>28825</v>
       </c>
@@ -7613,7 +7619,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>28856</v>
       </c>
@@ -7633,7 +7639,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>28887</v>
       </c>
@@ -7653,7 +7659,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>28915</v>
       </c>
@@ -7673,7 +7679,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>28946</v>
       </c>
@@ -7693,7 +7699,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>28976</v>
       </c>
@@ -7713,7 +7719,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>29007</v>
       </c>
@@ -7733,7 +7739,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>29037</v>
       </c>
@@ -7753,7 +7759,7 @@
         <v>0.109</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>29068</v>
       </c>
@@ -7773,7 +7779,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>29099</v>
       </c>
@@ -7793,7 +7799,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>29129</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>0.122</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>29160</v>
       </c>
@@ -7833,7 +7839,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>29190</v>
       </c>
@@ -7853,7 +7859,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>29221</v>
       </c>
@@ -7873,7 +7879,7 @@
         <v>0.13300000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>29252</v>
       </c>
@@ -7893,7 +7899,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>29281</v>
       </c>
@@ -7913,7 +7919,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>29312</v>
       </c>
@@ -7933,7 +7939,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>29342</v>
       </c>
@@ -7953,7 +7959,7 @@
         <v>0.14699999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>29373</v>
       </c>
@@ -7973,7 +7979,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>29403</v>
       </c>
@@ -7993,7 +7999,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>29434</v>
       </c>
@@ -8013,7 +8019,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>29465</v>
       </c>
@@ -8033,7 +8039,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>29495</v>
       </c>
@@ -8053,7 +8059,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>29526</v>
       </c>
@@ -8073,7 +8079,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>29556</v>
       </c>
@@ -8093,7 +8099,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>29587</v>
       </c>
@@ -8113,7 +8119,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>29618</v>
       </c>
@@ -8133,7 +8139,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>29646</v>
       </c>
@@ -8153,7 +8159,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>29677</v>
       </c>
@@ -8173,7 +8179,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>29707</v>
       </c>
@@ -8193,7 +8199,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>29738</v>
       </c>
@@ -8213,7 +8219,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>29768</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>29799</v>
       </c>
@@ -8253,7 +8259,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>29830</v>
       </c>
@@ -8273,7 +8279,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>29860</v>
       </c>
@@ -8293,7 +8299,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>29891</v>
       </c>
@@ -8313,7 +8319,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>29921</v>
       </c>
@@ -8333,7 +8339,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>29952</v>
       </c>
@@ -8353,7 +8359,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>29983</v>
       </c>
@@ -8373,7 +8379,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>30011</v>
       </c>
@@ -8393,7 +8399,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>30042</v>
       </c>
@@ -8413,7 +8419,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>30072</v>
       </c>
@@ -8433,7 +8439,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>30103</v>
       </c>
@@ -8453,7 +8459,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>30133</v>
       </c>
@@ -8473,7 +8479,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>30164</v>
       </c>
@@ -8493,7 +8499,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>30195</v>
       </c>
@@ -8513,7 +8519,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>30225</v>
       </c>
@@ -8533,7 +8539,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>30256</v>
       </c>
@@ -8553,7 +8559,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>30286</v>
       </c>
@@ -8573,7 +8579,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>30317</v>
       </c>
@@ -8593,7 +8599,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>30348</v>
       </c>
@@ -8613,7 +8619,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>30376</v>
       </c>
@@ -8633,7 +8639,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>30407</v>
       </c>
@@ -8653,7 +8659,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>30437</v>
       </c>
@@ -8673,7 +8679,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>30468</v>
       </c>
@@ -8693,7 +8699,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>30498</v>
       </c>
@@ -8713,7 +8719,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>30529</v>
       </c>
@@ -8733,7 +8739,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>30560</v>
       </c>
@@ -8753,7 +8759,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>30590</v>
       </c>
@@ -8773,7 +8779,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>30621</v>
       </c>
@@ -8793,7 +8799,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>30651</v>
       </c>
@@ -8813,7 +8819,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>30682</v>
       </c>
@@ -8833,7 +8839,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>30713</v>
       </c>
@@ -8853,7 +8859,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>30742</v>
       </c>
@@ -8873,7 +8879,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>30773</v>
       </c>
@@ -8893,7 +8899,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>30803</v>
       </c>
@@ -8913,7 +8919,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>30834</v>
       </c>
@@ -8933,7 +8939,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>30864</v>
       </c>
@@ -8953,7 +8959,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>30895</v>
       </c>
@@ -8973,7 +8979,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>30926</v>
       </c>
@@ -8993,7 +8999,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>30956</v>
       </c>
@@ -9013,7 +9019,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>30987</v>
       </c>
@@ -9033,7 +9039,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>31017</v>
       </c>
@@ -9053,7 +9059,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>31048</v>
       </c>
@@ -9073,7 +9079,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>31079</v>
       </c>
@@ -9093,7 +9099,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>31107</v>
       </c>
@@ -9113,7 +9119,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>31138</v>
       </c>
@@ -9133,7 +9139,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>31168</v>
       </c>
@@ -9153,7 +9159,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>31199</v>
       </c>
@@ -9173,7 +9179,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>31229</v>
       </c>
@@ -9193,7 +9199,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>31260</v>
       </c>
@@ -9213,7 +9219,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>31291</v>
       </c>
@@ -9233,7 +9239,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>31321</v>
       </c>
@@ -9253,7 +9259,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>31352</v>
       </c>
@@ -9273,7 +9279,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>31382</v>
       </c>
@@ -9293,7 +9299,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>31413</v>
       </c>
@@ -9313,7 +9319,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>31444</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>31472</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>31503</v>
       </c>
@@ -9373,7 +9379,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>31533</v>
       </c>
@@ -9393,7 +9399,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>31564</v>
       </c>
@@ -9413,7 +9419,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>31594</v>
       </c>
@@ -9433,7 +9439,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>31625</v>
       </c>
@@ -9453,7 +9459,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>31656</v>
       </c>
@@ -9473,7 +9479,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>31686</v>
       </c>
@@ -9493,7 +9499,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>31717</v>
       </c>
@@ -9513,7 +9519,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>31747</v>
       </c>
@@ -9533,7 +9539,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>31778</v>
       </c>
@@ -9553,7 +9559,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>31809</v>
       </c>
@@ -9573,7 +9579,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>31837</v>
       </c>
@@ -9593,7 +9599,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>31868</v>
       </c>
@@ -9613,7 +9619,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>31898</v>
       </c>
@@ -9633,7 +9639,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>31929</v>
       </c>
@@ -9653,7 +9659,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>31959</v>
       </c>
@@ -9673,7 +9679,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>31990</v>
       </c>
@@ -9693,7 +9699,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>32021</v>
       </c>
@@ -9713,7 +9719,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>32051</v>
       </c>
@@ -9733,7 +9739,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>32082</v>
       </c>
@@ -9753,7 +9759,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>32112</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>32143</v>
       </c>
@@ -9793,7 +9799,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>32174</v>
       </c>
@@ -9813,7 +9819,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>32203</v>
       </c>
@@ -9833,7 +9839,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>32234</v>
       </c>
@@ -9853,7 +9859,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>32264</v>
       </c>
@@ -9873,7 +9879,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>32295</v>
       </c>
@@ -9893,7 +9899,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>32325</v>
       </c>
@@ -9913,7 +9919,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>32356</v>
       </c>
@@ -9933,7 +9939,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>32387</v>
       </c>
@@ -9953,7 +9959,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>32417</v>
       </c>
@@ -9973,7 +9979,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>32448</v>
       </c>
@@ -9993,7 +9999,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>32478</v>
       </c>
@@ -10013,7 +10019,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>32509</v>
       </c>
@@ -10033,7 +10039,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>32540</v>
       </c>
@@ -10053,7 +10059,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>32568</v>
       </c>
@@ -10073,7 +10079,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>32599</v>
       </c>
@@ -10093,7 +10099,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>32629</v>
       </c>
@@ -10113,7 +10119,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>32660</v>
       </c>
@@ -10133,7 +10139,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>32690</v>
       </c>
@@ -10153,7 +10159,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>32721</v>
       </c>
@@ -10173,7 +10179,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>32752</v>
       </c>
@@ -10193,7 +10199,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>32782</v>
       </c>
@@ -10213,7 +10219,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>32813</v>
       </c>
@@ -10233,7 +10239,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>32843</v>
       </c>
@@ -10253,7 +10259,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>32874</v>
       </c>
@@ -10273,7 +10279,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>32905</v>
       </c>
@@ -10293,7 +10299,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>32933</v>
       </c>
@@ -10313,7 +10319,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>32964</v>
       </c>
@@ -10333,7 +10339,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>32994</v>
       </c>
@@ -10353,7 +10359,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>33025</v>
       </c>
@@ -10373,7 +10379,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>33055</v>
       </c>
@@ -10393,7 +10399,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>33086</v>
       </c>
@@ -10413,7 +10419,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>33117</v>
       </c>
@@ -10433,7 +10439,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>33147</v>
       </c>
@@ -10453,7 +10459,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>33178</v>
       </c>
@@ -10473,7 +10479,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>33208</v>
       </c>
@@ -10493,7 +10499,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>33239</v>
       </c>
@@ -10513,7 +10519,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>33270</v>
       </c>
@@ -10533,7 +10539,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>33298</v>
       </c>
@@ -10553,7 +10559,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>33329</v>
       </c>
@@ -10573,7 +10579,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>33359</v>
       </c>
@@ -10593,7 +10599,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>33390</v>
       </c>
@@ -10613,7 +10619,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>33420</v>
       </c>
@@ -10633,7 +10639,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>33451</v>
       </c>
@@ -10653,7 +10659,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>33482</v>
       </c>
@@ -10673,7 +10679,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>33512</v>
       </c>
@@ -10693,7 +10699,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>33543</v>
       </c>
@@ -10713,7 +10719,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>33573</v>
       </c>
@@ -10733,7 +10739,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>33604</v>
       </c>
@@ -10753,7 +10759,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>33635</v>
       </c>
@@ -10773,7 +10779,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>33664</v>
       </c>
@@ -10793,7 +10799,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>33695</v>
       </c>
@@ -10813,7 +10819,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>33725</v>
       </c>
@@ -10833,7 +10839,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>33756</v>
       </c>
@@ -10853,7 +10859,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>33786</v>
       </c>
@@ -10873,7 +10879,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>33817</v>
       </c>
@@ -10893,7 +10899,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>33848</v>
       </c>
@@ -10913,7 +10919,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>33878</v>
       </c>
@@ -10933,7 +10939,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>33909</v>
       </c>
@@ -10953,7 +10959,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>33939</v>
       </c>
@@ -10973,7 +10979,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>33970</v>
       </c>
@@ -10993,7 +10999,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>34001</v>
       </c>
@@ -11013,7 +11019,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>34029</v>
       </c>
@@ -11033,7 +11039,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>34060</v>
       </c>
@@ -11053,7 +11059,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>34090</v>
       </c>
@@ -11073,7 +11079,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>34121</v>
       </c>
@@ -11093,7 +11099,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>34151</v>
       </c>
@@ -11113,7 +11119,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>34182</v>
       </c>
@@ -11133,7 +11139,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>34213</v>
       </c>
@@ -11153,7 +11159,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>34243</v>
       </c>
@@ -11173,7 +11179,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>34274</v>
       </c>
@@ -11193,7 +11199,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>34304</v>
       </c>
@@ -11213,7 +11219,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>34335</v>
       </c>
@@ -11233,7 +11239,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>34366</v>
       </c>
@@ -11253,7 +11259,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>34394</v>
       </c>
@@ -11273,7 +11279,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>34425</v>
       </c>
@@ -11293,7 +11299,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>34455</v>
       </c>
@@ -11313,7 +11319,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>34486</v>
       </c>
@@ -11333,7 +11339,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>34516</v>
       </c>
@@ -11353,7 +11359,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>34547</v>
       </c>
@@ -11373,7 +11379,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>34578</v>
       </c>
@@ -11393,7 +11399,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>34608</v>
       </c>
@@ -11413,7 +11419,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>34639</v>
       </c>
@@ -11433,7 +11439,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>34669</v>
       </c>
@@ -11453,7 +11459,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>34700</v>
       </c>
@@ -11473,7 +11479,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="6">
         <v>34731</v>
       </c>
@@ -11493,7 +11499,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="6">
         <v>34759</v>
       </c>
@@ -11513,7 +11519,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="6">
         <v>34790</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="6">
         <v>34820</v>
       </c>
@@ -11553,7 +11559,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="6">
         <v>34851</v>
       </c>
@@ -11573,7 +11579,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="6">
         <v>34881</v>
       </c>
@@ -11593,7 +11599,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A310" s="6">
         <v>34912</v>
       </c>
@@ -11613,7 +11619,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="6">
         <v>34943</v>
       </c>
@@ -11633,7 +11639,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="6">
         <v>34973</v>
       </c>
@@ -11653,7 +11659,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="6">
         <v>35004</v>
       </c>
@@ -11673,7 +11679,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="6">
         <v>35034</v>
       </c>
@@ -11693,7 +11699,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="6">
         <v>35065</v>
       </c>
@@ -11713,7 +11719,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="6">
         <v>35096</v>
       </c>
@@ -11733,7 +11739,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A317" s="6">
         <v>35125</v>
       </c>
@@ -11753,7 +11759,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A318" s="6">
         <v>35156</v>
       </c>
@@ -11773,7 +11779,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="6">
         <v>35186</v>
       </c>
@@ -11793,7 +11799,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="6">
         <v>35217</v>
       </c>
@@ -11813,7 +11819,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="6">
         <v>35247</v>
       </c>
@@ -11833,7 +11839,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="6">
         <v>35278</v>
       </c>
@@ -11853,7 +11859,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323" s="6">
         <v>35309</v>
       </c>
@@ -11873,7 +11879,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324" s="6">
         <v>35339</v>
       </c>
@@ -11893,7 +11899,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325" s="6">
         <v>35370</v>
       </c>
@@ -11913,7 +11919,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326" s="6">
         <v>35400</v>
       </c>
@@ -11933,7 +11939,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="6">
         <v>35431</v>
       </c>
@@ -11953,7 +11959,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="6">
         <v>35462</v>
       </c>
@@ -11973,7 +11979,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="6">
         <v>35490</v>
       </c>
@@ -11993,7 +11999,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="6">
         <v>35521</v>
       </c>
@@ -12013,7 +12019,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331" s="6">
         <v>35551</v>
       </c>
@@ -12033,7 +12039,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332" s="6">
         <v>35582</v>
       </c>
@@ -12053,7 +12059,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="6">
         <v>35612</v>
       </c>
@@ -12073,7 +12079,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334" s="6">
         <v>35643</v>
       </c>
@@ -12093,7 +12099,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335" s="6">
         <v>35674</v>
       </c>
@@ -12113,7 +12119,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336" s="6">
         <v>35704</v>
       </c>
@@ -12133,7 +12139,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" s="6">
         <v>35735</v>
       </c>
@@ -12153,7 +12159,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="6">
         <v>35765</v>
       </c>
@@ -12173,7 +12179,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="6">
         <v>35796</v>
       </c>
@@ -12193,7 +12199,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A340" s="6">
         <v>35827</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" s="6">
         <v>35855</v>
       </c>
@@ -12233,7 +12239,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="6">
         <v>35886</v>
       </c>
@@ -12253,7 +12259,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" s="6">
         <v>35916</v>
       </c>
@@ -12273,7 +12279,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" s="6">
         <v>35947</v>
       </c>
@@ -12293,7 +12299,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="6">
         <v>35977</v>
       </c>
@@ -12313,7 +12319,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="6">
         <v>36008</v>
       </c>
@@ -12333,7 +12339,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" s="6">
         <v>36039</v>
       </c>
@@ -12353,7 +12359,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" s="6">
         <v>36069</v>
       </c>
@@ -12373,7 +12379,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" s="6">
         <v>36100</v>
       </c>
@@ -12393,7 +12399,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" s="6">
         <v>36130</v>
       </c>
@@ -12413,7 +12419,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" s="6">
         <v>36161</v>
       </c>
@@ -12433,7 +12439,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" s="6">
         <v>36192</v>
       </c>
@@ -12453,7 +12459,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A353" s="6">
         <v>36220</v>
       </c>
@@ -12473,7 +12479,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A354" s="6">
         <v>36251</v>
       </c>
@@ -12493,7 +12499,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A355" s="6">
         <v>36281</v>
       </c>
@@ -12513,7 +12519,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A356" s="6">
         <v>36312</v>
       </c>
@@ -12533,7 +12539,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A357" s="6">
         <v>36342</v>
       </c>
@@ -12553,7 +12559,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A358" s="6">
         <v>36373</v>
       </c>
@@ -12573,7 +12579,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A359" s="6">
         <v>36404</v>
       </c>
@@ -12593,7 +12599,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A360" s="6">
         <v>36434</v>
       </c>
@@ -12613,7 +12619,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A361" s="6">
         <v>36465</v>
       </c>
@@ -12633,7 +12639,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" s="6">
         <v>36495</v>
       </c>
@@ -12653,7 +12659,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A363" s="6">
         <v>36526</v>
       </c>
@@ -12673,7 +12679,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A364" s="6">
         <v>36557</v>
       </c>
@@ -12693,7 +12699,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" s="6">
         <v>36586</v>
       </c>
@@ -12713,7 +12719,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A366" s="6">
         <v>36617</v>
       </c>
@@ -12733,7 +12739,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A367" s="6">
         <v>36647</v>
       </c>
@@ -12753,7 +12759,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A368" s="6">
         <v>36678</v>
       </c>
@@ -12773,7 +12779,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A369" s="6">
         <v>36708</v>
       </c>
@@ -12793,7 +12799,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A370" s="6">
         <v>36739</v>
       </c>
@@ -12813,7 +12819,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A371" s="6">
         <v>36770</v>
       </c>
@@ -12833,7 +12839,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A372" s="6">
         <v>36800</v>
       </c>
@@ -12853,7 +12859,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A373" s="6">
         <v>36831</v>
       </c>
@@ -12873,7 +12879,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A374" s="6">
         <v>36861</v>
       </c>
@@ -12893,7 +12899,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A375" s="6">
         <v>36892</v>
       </c>
@@ -12913,7 +12919,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A376" s="6">
         <v>36923</v>
       </c>
@@ -12933,7 +12939,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A377" s="6">
         <v>36951</v>
       </c>
@@ -12953,7 +12959,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A378" s="6">
         <v>36982</v>
       </c>
@@ -12973,7 +12979,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A379" s="6">
         <v>37012</v>
       </c>
@@ -12993,7 +12999,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A380" s="6">
         <v>37043</v>
       </c>
@@ -13013,7 +13019,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A381" s="6">
         <v>37073</v>
       </c>
@@ -13033,7 +13039,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A382" s="6">
         <v>37104</v>
       </c>
@@ -13053,7 +13059,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A383" s="6">
         <v>37135</v>
       </c>
@@ -13073,7 +13079,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A384" s="6">
         <v>37165</v>
       </c>
@@ -13093,7 +13099,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A385" s="6">
         <v>37196</v>
       </c>
@@ -13113,7 +13119,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A386" s="6">
         <v>37226</v>
       </c>
@@ -13133,7 +13139,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A387" s="6">
         <v>37257</v>
       </c>
@@ -13153,7 +13159,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A388" s="6">
         <v>37288</v>
       </c>
@@ -13173,7 +13179,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A389" s="6">
         <v>37316</v>
       </c>
@@ -13193,7 +13199,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A390" s="6">
         <v>37347</v>
       </c>
@@ -13213,7 +13219,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A391" s="6">
         <v>37377</v>
       </c>
@@ -13233,7 +13239,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A392" s="6">
         <v>37408</v>
       </c>
@@ -13253,7 +13259,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A393" s="6">
         <v>37438</v>
       </c>
@@ -13273,7 +13279,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A394" s="6">
         <v>37469</v>
       </c>
@@ -13293,7 +13299,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A395" s="6">
         <v>37500</v>
       </c>
@@ -13313,7 +13319,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A396" s="6">
         <v>37530</v>
       </c>
@@ -13333,7 +13339,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A397" s="6">
         <v>37561</v>
       </c>
@@ -13353,7 +13359,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A398" s="6">
         <v>37591</v>
       </c>
@@ -13373,7 +13379,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A399" s="6">
         <v>37622</v>
       </c>
@@ -13393,7 +13399,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A400" s="6">
         <v>37653</v>
       </c>
@@ -13413,7 +13419,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A401" s="6">
         <v>37681</v>
       </c>
@@ -13433,7 +13439,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A402" s="6">
         <v>37712</v>
       </c>
@@ -13453,7 +13459,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A403" s="6">
         <v>37742</v>
       </c>
@@ -13473,7 +13479,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A404" s="6">
         <v>37773</v>
       </c>
@@ -13493,7 +13499,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A405" s="6">
         <v>37803</v>
       </c>
@@ -13513,7 +13519,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A406" s="6">
         <v>37834</v>
       </c>
@@ -13533,7 +13539,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A407" s="6">
         <v>37865</v>
       </c>
@@ -13553,7 +13559,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A408" s="6">
         <v>37895</v>
       </c>
@@ -13573,7 +13579,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A409" s="6">
         <v>37926</v>
       </c>
@@ -13593,7 +13599,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A410" s="6">
         <v>37956</v>
       </c>
@@ -13613,7 +13619,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A411" s="6">
         <v>37987</v>
       </c>
@@ -13633,7 +13639,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A412" s="6">
         <v>38018</v>
       </c>
@@ -13653,7 +13659,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A413" s="6">
         <v>38047</v>
       </c>
@@ -13673,7 +13679,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A414" s="6">
         <v>38078</v>
       </c>
@@ -13693,7 +13699,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A415" s="6">
         <v>38108</v>
       </c>
@@ -13713,7 +13719,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A416" s="6">
         <v>38139</v>
       </c>
@@ -13733,7 +13739,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A417" s="6">
         <v>38169</v>
       </c>
@@ -13753,7 +13759,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A418" s="6">
         <v>38200</v>
       </c>
@@ -13773,7 +13779,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A419" s="6">
         <v>38231</v>
       </c>
@@ -13793,7 +13799,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A420" s="6">
         <v>38261</v>
       </c>
@@ -13813,7 +13819,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A421" s="6">
         <v>38292</v>
       </c>
@@ -13833,7 +13839,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A422" s="6">
         <v>38322</v>
       </c>
@@ -13853,7 +13859,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A423" s="6">
         <v>38353</v>
       </c>
@@ -13873,7 +13879,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A424" s="6">
         <v>38384</v>
       </c>
@@ -13893,7 +13899,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A425" s="6">
         <v>38412</v>
       </c>
@@ -13913,7 +13919,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A426" s="6">
         <v>38443</v>
       </c>
@@ -13933,7 +13939,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A427" s="6">
         <v>38473</v>
       </c>
@@ -13953,7 +13959,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A428" s="6">
         <v>38504</v>
       </c>
@@ -13973,7 +13979,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A429" s="6">
         <v>38534</v>
       </c>
@@ -13993,7 +13999,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A430" s="6">
         <v>38565</v>
       </c>
@@ -14013,7 +14019,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A431" s="6">
         <v>38596</v>
       </c>
@@ -14033,7 +14039,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A432" s="6">
         <v>38626</v>
       </c>
@@ -14053,7 +14059,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A433" s="6">
         <v>38657</v>
       </c>
@@ -14073,7 +14079,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A434" s="6">
         <v>38687</v>
       </c>
@@ -14093,7 +14099,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A435" s="6">
         <v>38718</v>
       </c>
@@ -14113,7 +14119,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A436" s="6">
         <v>38749</v>
       </c>
@@ -14133,7 +14139,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A437" s="6">
         <v>38777</v>
       </c>
@@ -14153,7 +14159,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A438" s="6">
         <v>38808</v>
       </c>
@@ -14173,7 +14179,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A439" s="6">
         <v>38838</v>
       </c>
@@ -14193,7 +14199,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A440" s="6">
         <v>38869</v>
       </c>
@@ -14213,7 +14219,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A441" s="6">
         <v>38899</v>
       </c>
@@ -14233,7 +14239,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A442" s="6">
         <v>38930</v>
       </c>
@@ -14253,7 +14259,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A443" s="6">
         <v>38961</v>
       </c>
@@ -14273,7 +14279,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A444" s="6">
         <v>38991</v>
       </c>
@@ -14293,7 +14299,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A445" s="6">
         <v>39022</v>
       </c>
@@ -14313,7 +14319,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A446" s="6">
         <v>39052</v>
       </c>
@@ -14333,7 +14339,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A447" s="6">
         <v>39083</v>
       </c>
@@ -14353,7 +14359,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A448" s="6">
         <v>39114</v>
       </c>
@@ -14373,7 +14379,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A449" s="6">
         <v>39142</v>
       </c>
@@ -14393,7 +14399,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A450" s="6">
         <v>39173</v>
       </c>
@@ -14413,7 +14419,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A451" s="6">
         <v>39203</v>
       </c>
@@ -14433,7 +14439,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A452" s="6">
         <v>39234</v>
       </c>
@@ -14453,7 +14459,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A453" s="6">
         <v>39264</v>
       </c>
@@ -14473,7 +14479,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A454" s="6">
         <v>39295</v>
       </c>
@@ -14493,7 +14499,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A455" s="6">
         <v>39326</v>
       </c>
@@ -14513,7 +14519,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A456" s="6">
         <v>39356</v>
       </c>
@@ -14533,7 +14539,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A457" s="6">
         <v>39387</v>
       </c>
@@ -14553,7 +14559,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A458" s="6">
         <v>39417</v>
       </c>
@@ -14573,7 +14579,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A459" s="6">
         <v>39448</v>
       </c>
@@ -14593,7 +14599,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A460" s="6">
         <v>39479</v>
       </c>
@@ -14613,7 +14619,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A461" s="6">
         <v>39508</v>
       </c>
@@ -14633,7 +14639,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A462" s="6">
         <v>39539</v>
       </c>
@@ -14653,7 +14659,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A463" s="6">
         <v>39569</v>
       </c>
@@ -14673,7 +14679,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A464" s="6">
         <v>39600</v>
       </c>
@@ -14693,7 +14699,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A465" s="6">
         <v>39630</v>
       </c>
@@ -14713,7 +14719,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A466" s="6">
         <v>39661</v>
       </c>
@@ -14733,7 +14739,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A467" s="6">
         <v>39692</v>
       </c>
@@ -14753,7 +14759,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A468" s="6">
         <v>39722</v>
       </c>
@@ -14773,7 +14779,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A469" s="6">
         <v>39753</v>
       </c>
@@ -14793,7 +14799,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A470" s="6">
         <v>39783</v>
       </c>
@@ -14813,7 +14819,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A471" s="6">
         <v>39814</v>
       </c>
@@ -14833,7 +14839,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A472" s="6">
         <v>39845</v>
       </c>
@@ -14853,7 +14859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A473" s="6">
         <v>39873</v>
       </c>
@@ -14873,7 +14879,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A474" s="6">
         <v>39904</v>
       </c>
@@ -14893,7 +14899,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A475" s="6">
         <v>39934</v>
       </c>
@@ -14913,7 +14919,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A476" s="6">
         <v>39965</v>
       </c>
@@ -14933,7 +14939,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A477" s="6">
         <v>39995</v>
       </c>
@@ -14953,7 +14959,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A478" s="6">
         <v>40026</v>
       </c>
@@ -14973,7 +14979,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A479" s="6">
         <v>40057</v>
       </c>
@@ -14993,7 +14999,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A480" s="6">
         <v>40087</v>
       </c>
@@ -15013,7 +15019,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481" s="6">
         <v>40118</v>
       </c>
@@ -15033,7 +15039,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482" s="6">
         <v>40148</v>
       </c>
@@ -15053,7 +15059,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483" s="6">
         <v>40179</v>
       </c>
@@ -15073,7 +15079,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484" s="6">
         <v>40210</v>
       </c>
@@ -15093,7 +15099,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485" s="6">
         <v>40238</v>
       </c>
@@ -15113,7 +15119,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486" s="6">
         <v>40269</v>
       </c>
@@ -15133,7 +15139,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487" s="6">
         <v>40299</v>
       </c>
@@ -15153,7 +15159,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488" s="6">
         <v>40330</v>
       </c>
@@ -15173,7 +15179,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489" s="6">
         <v>40360</v>
       </c>
@@ -15193,7 +15199,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490" s="6">
         <v>40391</v>
       </c>
@@ -15213,7 +15219,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491" s="6">
         <v>40422</v>
       </c>
@@ -15233,7 +15239,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492" s="6">
         <v>40452</v>
       </c>
@@ -15253,7 +15259,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493" s="6">
         <v>40483</v>
       </c>
@@ -15273,7 +15279,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494" s="6">
         <v>40513</v>
       </c>
@@ -15293,7 +15299,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495" s="6">
         <v>40544</v>
       </c>
@@ -15313,7 +15319,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496" s="6">
         <v>40575</v>
       </c>
@@ -15333,7 +15339,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497" s="6">
         <v>40603</v>
       </c>
@@ -15353,7 +15359,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498" s="6">
         <v>40634</v>
       </c>
@@ -15373,7 +15379,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499" s="6">
         <v>40664</v>
       </c>
@@ -15393,7 +15399,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500" s="6">
         <v>40695</v>
       </c>
@@ -15413,7 +15419,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501" s="6">
         <v>40725</v>
       </c>
@@ -15433,7 +15439,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A502" s="6">
         <v>40756</v>
       </c>
@@ -15453,7 +15459,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A503" s="6">
         <v>40787</v>
       </c>
@@ -15473,7 +15479,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A504" s="6">
         <v>40817</v>
       </c>
@@ -15493,7 +15499,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A505" s="6">
         <v>40848</v>
       </c>
@@ -15513,7 +15519,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A506" s="6">
         <v>40878</v>
       </c>
@@ -15533,7 +15539,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A507" s="6">
         <v>40909</v>
       </c>
@@ -15553,7 +15559,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A508" s="6">
         <v>40940</v>
       </c>
@@ -15573,7 +15579,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A509" s="6">
         <v>40969</v>
       </c>
@@ -15593,7 +15599,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A510" s="6">
         <v>41000</v>
       </c>
@@ -15616,7 +15622,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A511" s="6">
         <v>41030</v>
       </c>
@@ -15639,7 +15645,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A512" s="6">
         <v>41061</v>
       </c>
@@ -15662,7 +15668,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A513" s="6">
         <v>41091</v>
       </c>
@@ -15685,7 +15691,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A514" s="6">
         <v>41122</v>
       </c>
@@ -15708,7 +15714,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A515" s="6">
         <v>41153</v>
       </c>
@@ -15731,7 +15737,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A516" s="6">
         <v>41183</v>
       </c>
@@ -15754,7 +15760,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A517" s="6">
         <v>41214</v>
       </c>
@@ -15777,7 +15783,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A518" s="6">
         <v>41244</v>
       </c>
@@ -15800,7 +15806,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A519" s="6">
         <v>41275</v>
       </c>
@@ -15823,7 +15829,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A520" s="6">
         <v>41306</v>
       </c>
@@ -15846,7 +15852,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A521" s="6">
         <v>41334</v>
       </c>
@@ -15869,7 +15875,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A522" s="6">
         <v>41365</v>
       </c>
@@ -15892,7 +15898,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A523" s="6">
         <v>41395</v>
       </c>
@@ -15915,7 +15921,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A524" s="6">
         <v>41426</v>
       </c>
@@ -15938,7 +15944,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A525" s="6">
         <v>41456</v>
       </c>
@@ -15961,7 +15967,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A526" s="6">
         <v>41487</v>
       </c>
@@ -15984,7 +15990,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A527" s="6">
         <v>41518</v>
       </c>
@@ -16007,7 +16013,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A528" s="6">
         <v>41548</v>
       </c>
@@ -16030,7 +16036,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A529" s="6">
         <v>41579</v>
       </c>
@@ -16053,7 +16059,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A530" s="6">
         <v>41609</v>
       </c>
@@ -16076,7 +16082,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A531" s="6">
         <v>41640</v>
       </c>
@@ -16099,7 +16105,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A532" s="6">
         <v>41671</v>
       </c>
@@ -16122,7 +16128,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A533" s="6">
         <v>41699</v>
       </c>
@@ -16145,7 +16151,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A534" s="6">
         <v>41730</v>
       </c>
@@ -16168,7 +16174,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535" s="6">
         <v>41760</v>
       </c>
@@ -16191,7 +16197,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536" s="6">
         <v>41791</v>
       </c>
@@ -16214,7 +16220,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537" s="6">
         <v>41821</v>
       </c>
@@ -16237,7 +16243,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538" s="6">
         <v>41852</v>
       </c>
@@ -16260,7 +16266,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539" s="6">
         <v>41883</v>
       </c>
@@ -16283,7 +16289,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A540" s="6">
         <v>41913</v>
       </c>
@@ -16306,7 +16312,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="541" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A541" s="6">
         <v>41944</v>
       </c>
@@ -16329,7 +16335,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A542" s="6">
         <v>41974</v>
       </c>
@@ -16352,7 +16358,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A543" s="6">
         <v>42005</v>
       </c>
@@ -16375,7 +16381,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A544" s="6">
         <v>42036</v>
       </c>
@@ -16398,7 +16404,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A545" s="6">
         <v>42064</v>
       </c>
@@ -16421,7 +16427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A546" s="6">
         <v>42095</v>
       </c>
@@ -16444,7 +16450,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A547" s="6">
         <v>42125</v>
       </c>
@@ -16467,7 +16473,7 @@
         <v>-2E-3</v>
       </c>
     </row>
-    <row r="548" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A548" s="6">
         <v>42156</v>
       </c>
@@ -16490,7 +16496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A549" s="6">
         <v>42186</v>
       </c>
@@ -16513,7 +16519,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A550" s="6">
         <v>42217</v>
       </c>
@@ -16536,7 +16542,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551" s="6">
         <v>42248</v>
       </c>
@@ -16559,7 +16565,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="552" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552" s="6">
         <v>42278</v>
       </c>
@@ -16582,7 +16588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553" s="6">
         <v>42309</v>
       </c>
@@ -16605,7 +16611,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="554" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554" s="6">
         <v>42339</v>
       </c>
@@ -16628,7 +16634,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="555" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555" s="6">
         <v>42370</v>
       </c>
@@ -16651,7 +16657,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="556" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556" s="6">
         <v>42401</v>
       </c>
@@ -16674,7 +16680,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="557" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557" s="6">
         <v>42430</v>
       </c>
@@ -16697,7 +16703,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="558" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558" s="6">
         <v>42461</v>
       </c>
@@ -16720,7 +16726,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="559" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559" s="6">
         <v>42491</v>
       </c>
@@ -16743,7 +16749,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560" s="6">
         <v>42522</v>
       </c>
@@ -16766,7 +16772,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="561" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561" s="6">
         <v>42552</v>
       </c>
@@ -16789,7 +16795,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="562" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562" s="6">
         <v>42583</v>
       </c>
@@ -16812,7 +16818,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="563" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563" s="6">
         <v>42614</v>
       </c>
@@ -16835,7 +16841,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="564" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564" s="6">
         <v>42644</v>
       </c>
@@ -16858,7 +16864,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565" s="6">
         <v>42675</v>
       </c>
@@ -16881,7 +16887,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="566" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566" s="6">
         <v>42705</v>
       </c>
@@ -16904,7 +16910,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="567" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567" s="6">
         <v>42736</v>
       </c>
@@ -16927,7 +16933,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="568" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568" s="6">
         <v>42767</v>
       </c>
@@ -16950,7 +16956,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="569" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569" s="6">
         <v>42795</v>
       </c>
@@ -16973,7 +16979,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="570" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570" s="6">
         <v>42826</v>
       </c>
@@ -16996,7 +17002,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="571" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571" s="6">
         <v>42856</v>
       </c>
@@ -17019,7 +17025,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="572" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572" s="6">
         <v>42887</v>
       </c>
@@ -17042,7 +17048,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="573" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573" s="6">
         <v>42917</v>
       </c>
@@ -17065,7 +17071,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="574" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574" s="6">
         <v>42948</v>
       </c>
@@ -17088,7 +17094,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="575" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575" s="6">
         <v>42979</v>
       </c>
@@ -17111,7 +17117,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="576" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576" s="6">
         <v>43009</v>
       </c>
@@ -17134,7 +17140,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="577" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577" s="6">
         <v>43040</v>
       </c>
@@ -17157,7 +17163,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="578" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578" s="6">
         <v>43070</v>
       </c>
@@ -17180,7 +17186,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="579" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579" s="6">
         <v>43101</v>
       </c>
@@ -17203,7 +17209,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="580" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580" s="6">
         <v>43132</v>
       </c>
@@ -17226,7 +17232,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="581" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581" s="6">
         <v>43160</v>
       </c>
@@ -17249,7 +17255,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582" s="6">
         <v>43191</v>
       </c>
@@ -17272,7 +17278,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="583" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583" s="6">
         <v>43221</v>
       </c>
@@ -17295,7 +17301,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="584" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584" s="6">
         <v>43252</v>
       </c>
@@ -17318,7 +17324,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="585" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585" s="6">
         <v>43282</v>
       </c>
@@ -17341,7 +17347,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="586" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586" s="6">
         <v>43313</v>
       </c>
@@ -17364,7 +17370,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587" s="6">
         <v>43344</v>
       </c>
@@ -17387,7 +17393,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588" s="6">
         <v>43374</v>
       </c>
@@ -17410,7 +17416,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="589" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589" s="6">
         <v>43405</v>
       </c>
@@ -17433,7 +17439,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="590" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590" s="6">
         <v>43435</v>
       </c>
@@ -17456,7 +17462,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="591" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591" s="6">
         <v>43466</v>
       </c>
@@ -17479,7 +17485,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="592" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592" s="6">
         <v>43497</v>
       </c>
@@ -17502,7 +17508,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593" s="6">
         <v>43525</v>
       </c>
@@ -17525,7 +17531,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="594" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594" s="6">
         <v>43556</v>
       </c>
@@ -17548,7 +17554,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="595" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A595" s="6">
         <v>43586</v>
       </c>
@@ -17571,7 +17577,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="596" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A596" s="6">
         <v>43617</v>
       </c>
@@ -17594,7 +17600,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="597" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A597" s="6">
         <v>43647</v>
       </c>
@@ -17617,7 +17623,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="598" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A598" s="6">
         <v>43678</v>
       </c>
@@ -17640,7 +17646,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A599" s="6">
         <v>43709</v>
       </c>
@@ -17663,7 +17669,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="600" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A600" s="6">
         <v>43739</v>
       </c>
@@ -17686,7 +17692,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="601" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A601" s="6">
         <v>43770</v>
       </c>
@@ -17709,7 +17715,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="602" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A602" s="6">
         <v>43800</v>
       </c>
@@ -17732,7 +17738,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="603" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A603" s="6">
         <v>43831</v>
       </c>
@@ -17755,7 +17761,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A604" s="6">
         <v>43862</v>
       </c>
@@ -17778,7 +17784,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A605" s="6">
         <v>43891</v>
       </c>
@@ -17801,7 +17807,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A606" s="6">
         <v>43922</v>
       </c>
@@ -17824,7 +17830,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A607" s="6">
         <v>43952</v>
       </c>
@@ -17847,7 +17853,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="608" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A608" s="6">
         <v>43983</v>
       </c>
@@ -17870,7 +17876,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="609" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A609" s="6">
         <v>44013</v>
       </c>
@@ -17893,7 +17899,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="610" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A610" s="6">
         <v>44044</v>
       </c>
@@ -17916,7 +17922,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="611" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A611" s="6">
         <v>44075</v>
       </c>
@@ -17939,7 +17945,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="612" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A612" s="6">
         <v>44105</v>
       </c>
@@ -17962,7 +17968,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="613" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A613" s="6">
         <v>44136</v>
       </c>
@@ -17985,7 +17991,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="614" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A614" s="6">
         <v>44166</v>
       </c>
@@ -18008,7 +18014,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="615" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A615" s="6">
         <v>44197</v>
       </c>
@@ -18031,7 +18037,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="616" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A616" s="6">
         <v>44228</v>
       </c>
@@ -18054,7 +18060,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="617" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A617" s="6">
         <v>44256</v>
       </c>
@@ -18077,7 +18083,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A618" s="6">
         <v>44287</v>
       </c>
@@ -18100,7 +18106,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="619" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A619" s="6">
         <v>44317</v>
       </c>
@@ -18123,7 +18129,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="620" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A620" s="6">
         <v>44348</v>
       </c>
@@ -18146,7 +18152,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="621" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A621" s="6">
         <v>44378</v>
       </c>
@@ -18169,7 +18175,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="622" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A622" s="6">
         <v>44409</v>
       </c>
@@ -18192,7 +18198,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="623" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A623" s="6">
         <v>44440</v>
       </c>
@@ -18215,7 +18221,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="624" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A624" s="6">
         <v>44470</v>
       </c>
@@ -18238,7 +18244,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="625" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A625" s="6">
         <v>44501</v>
       </c>
@@ -18261,7 +18267,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="626" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A626" s="6">
         <v>44531</v>
       </c>
@@ -18284,7 +18290,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="627" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A627" s="6">
         <v>44562</v>
       </c>
@@ -18307,7 +18313,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="628" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A628" s="6">
         <v>44593</v>
       </c>
@@ -18330,7 +18336,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="629" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A629" s="6">
         <v>44621</v>
       </c>
@@ -18353,7 +18359,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="630" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A630" s="6">
         <v>44652</v>
       </c>
@@ -18376,7 +18382,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="631" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A631" s="6">
         <v>44682</v>
       </c>
@@ -18399,7 +18405,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="632" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A632" s="6">
         <v>44713</v>
       </c>
@@ -18422,7 +18428,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="633" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A633" s="6">
         <v>44743</v>
       </c>
@@ -18445,7 +18451,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="634" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A634" s="6">
         <v>44774</v>
       </c>
@@ -18468,7 +18474,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="635" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A635" s="6">
         <v>44805</v>
       </c>
@@ -18491,7 +18497,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="636" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A636" s="6">
         <v>44835</v>
       </c>
@@ -18514,7 +18520,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="637" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A637" s="6">
         <v>44866</v>
       </c>
@@ -18537,7 +18543,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="638" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A638" s="6">
         <v>44896</v>
       </c>
@@ -18560,7 +18566,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="639" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A639" s="6">
         <v>44927</v>
       </c>
@@ -18583,7 +18589,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="640" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A640" s="6">
         <v>44958</v>
       </c>
@@ -18606,7 +18612,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A641" s="6">
         <v>44986</v>
       </c>
@@ -18629,7 +18635,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="642" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A642" s="6">
         <v>45017</v>
       </c>
@@ -18652,7 +18658,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="643" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A643" s="6">
         <v>45047</v>
       </c>
@@ -18675,7 +18681,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="644" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A644" s="6">
         <v>45078</v>
       </c>
@@ -18698,7 +18704,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="645" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A645" s="6">
         <v>45108</v>
       </c>
@@ -18721,7 +18727,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="646" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A646" s="6">
         <v>45139</v>
       </c>
@@ -18744,7 +18750,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="647" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A647" s="6">
         <v>45170</v>
       </c>
@@ -18767,7 +18773,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="648" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A648" s="6">
         <v>45200</v>
       </c>
@@ -18790,7 +18796,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="649" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A649" s="6">
         <v>45231</v>
       </c>
@@ -18813,7 +18819,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="650" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A650" s="6">
         <v>45261</v>
       </c>
@@ -18836,7 +18842,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="651" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A651" s="6">
         <v>45292</v>
       </c>
@@ -18859,7 +18865,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="652" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A652" s="6">
         <v>45323</v>
       </c>
@@ -18882,7 +18888,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="653" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A653" s="6">
         <v>45352</v>
       </c>
@@ -18905,7 +18911,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="654" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A654" s="6">
         <v>45383</v>
       </c>
@@ -18928,7 +18934,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="655" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A655" s="6">
         <v>45413</v>
       </c>
@@ -18951,7 +18957,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="656" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A656" s="6">
         <v>45444</v>
       </c>
@@ -18974,7 +18980,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="657" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A657" s="6">
         <v>45474</v>
       </c>
@@ -18997,7 +19003,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="658" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A658" s="6">
         <v>45505</v>
       </c>
@@ -19020,7 +19026,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="659" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A659" s="6">
         <v>45536</v>
       </c>
@@ -19043,7 +19049,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="660" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A660" s="6">
         <v>45566</v>
       </c>
@@ -19066,7 +19072,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="661" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A661" s="6">
         <v>45597</v>
       </c>
@@ -19089,7 +19095,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="662" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A662" s="6">
         <v>45627</v>
       </c>
@@ -19112,7 +19118,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="663" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A663" s="6">
         <v>45658</v>
       </c>
@@ -19135,7 +19141,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="664" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A664" s="6">
         <v>45689</v>
       </c>
@@ -19158,7 +19164,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="665" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A665" s="6">
         <v>45717</v>
       </c>
@@ -19181,7 +19187,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="666" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A666" s="6">
         <v>45748</v>
       </c>
@@ -19204,7 +19210,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="667" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A667" s="6">
         <v>45778</v>
       </c>
@@ -19227,7 +19233,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="668" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A668" s="6">
         <v>45809</v>
       </c>
@@ -19250,7 +19256,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="669" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A669" s="6">
         <v>45839</v>
       </c>
@@ -19273,7 +19279,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="670" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A670" s="6">
         <v>45870</v>
       </c>
@@ -19296,7 +19302,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="671" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A671" s="6">
         <v>45901</v>
       </c>
@@ -19319,7 +19325,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="672" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A672" s="6">
         <v>45962</v>
       </c>
@@ -19342,7 +19348,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="673" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A673" s="6">
         <v>45992</v>
       </c>
@@ -19365,7 +19371,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="674" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A674" s="6">
         <v>46023</v>
       </c>
@@ -19388,7 +19394,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="675" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A675" s="6">
         <v>46054</v>
       </c>
@@ -19432,6 +19438,29 @@
       </c>
       <c r="G676" s="9">
         <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B677" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C677" s="14">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D677" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E677" s="9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="F677" s="9">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="G677" s="9">
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
   </sheetData>
